--- a/results/Int Task Remove ACC -0.7/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.005073349633251856 +/- 0.0010427091753809346</t>
+          <t>0.00357579462102684 +/- 0.0011023648408845538</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.006051344743276299 +/- 0.0012952090525927286</t>
+          <t>-0.0037286063569682893 +/- 0.001610261598083061</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.004676039119804432 +/- 0.002122048329687029</t>
+          <t>-9.168704156483631e-05 +/- 0.0012380580134797663</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0009474327628362089 +/- 0.0005543507685579875</t>
+          <t>0.0001833740831295394 +/- 0.0011451707821024024</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.001864303178484128 +/- 0.0011141641890928138</t>
+          <t>3.0562347188212156e-05 +/- 0.0013698615422380934</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0028422982885085712 +/- 0.0016686593758824786</t>
+          <t>-0.0004889975550122827 +/- 0.0014018759096796752</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.00033618581907091105 +/- 0.00021393643031783087</t>
+          <t>-0.00036674816625921204 +/- 0.00012224938875307067</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0018948655256723844 +/- 0.0012879772314000918</t>
+          <t>0.0005501222493886959 +/- 0.0013790359624301293</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.018490220048899764 +/- 0.002665239948731406</t>
+          <t>0.019070904645476717 +/- 0.002460980701613368</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.026925427872860664 +/- 0.002697289469892782</t>
+          <t>0.02038508557457208 +/- 0.00231569031045411</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.00024449877750611917 +/- 0.0022241326893227722</t>
+          <t>-0.0022921760391198644 +/- 0.000968879430571355</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0039425427872860856 +/- 0.0013423099789729644</t>
+          <t>-0.0017726161369193694 +/- 0.000560217077622958</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.011735941320293408 +/- 0.00198160942267083</t>
+          <t>-0.0006723716381418666 +/- 0.001344743276283627</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.009260391198044005 +/- 0.0017506116737921382</t>
+          <t>0.01051344743276278 +/- 0.002213186673622459</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.016106356968215198 +/- 0.0023517125431797617</t>
+          <t>0.019926650366748122 +/- 0.0035346778226897062</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0007640586797065918 +/- 0.0010159394950241417</t>
+          <t>-0.0028728606356968832 +/- 0.001388486148117412</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0020476772616137007 +/- 0.0014272976074371278</t>
+          <t>-0.00012224938875310398 +/- 0.0010154796898432978</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.002047677261613712 +/- 0.0011108057362705776</t>
+          <t>0.00033618581907086665 +/- 0.0014558075016888313</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.006754278728606377 +/- 0.001233522987201143</t>
+          <t>0.0022616136919314965 +/- 0.0008447600831959284</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00012224938875305958 +/- 0.00020272767667208765</t>
+          <t>0.00015281173594128283 +/- 0.0002464015204247532</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0256112469437653 +/- 0.0017005412889050811</t>
+          <t>0.016564792176039067 +/- 0.0014644435881064786</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.000672371638141811 +/- 0.0009931587291731098</t>
+          <t>0.0005501222493887071 +/- 0.0012055674158506083</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.0053484107579462314 +/- 0.001201298533437235</t>
+          <t>0.00021393643031779596 +/- 0.000875705915763711</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0008251833740831494 +/- 0.0009955071806175236</t>
+          <t>-0.0006112469437653312 +/- 0.0009950379337469513</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0018948655256723513 +/- 0.0011087015371159515</t>
+          <t>-0.0014364303178484583 +/- 0.0007366730313688352</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-6.112469437652424e-05 +/- 0.0004695076863000363</t>
+          <t>-0.00033618581907094434 +/- 0.0004624922356485985</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0047677261613692234 +/- 0.0009969135959840942</t>
+          <t>0.0017114914425427452 +/- 0.001529339364693998</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.002750611246943746 +/- 0.001452917399022573</t>
+          <t>0.0034535452322737915 +/- 0.0010323560974360942</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.0013447432762836442 +/- 0.0013405692053460618</t>
+          <t>-0.001558679706601529 +/- 0.0012708204698222295</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0019254278728606411 +/- 0.0011191829721027193</t>
+          <t>-0.00889364303178487 +/- 0.0012634490592050326</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.000672371638141811 +/- 0.0005432881673175768</t>
+          <t>-0.00045843520782402615 +/- 0.0003416974293245555</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.00036674816625916764 +/- 0.0005077398449216547</t>
+          <t>-0.0009474327628362644 +/- 0.00021393643031783087</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.0011308068459657706 +/- 0.0011520829355116358</t>
+          <t>-0.0071821515892421025 +/- 0.0019723964303499375</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.002017114914425444 +/- 0.0014669926650366864</t>
+          <t>0.000886308068459607 +/- 0.000999253222755009</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0007334963325183574 +/- 0.000787536596988097</t>
+          <t>-0.00024449877750615245 +/- 0.00035641515249668147</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.00033618581907089994 +/- 0.00039731051344743187</t>
+          <t>-0.00015281173594137166 +/- 0.0007392045612743377</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0047677261613692234 +/- 0.0013335833880972724</t>
+          <t>-0.0018643031784841835 +/- 0.001390166921215664</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.0017726161369193028 +/- 0.0013377792560048422</t>
+          <t>-0.0063875305623472545 +/- 0.001270820469822218</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.00018337408312958382 +/- 0.000725815530992545</t>
+          <t>0.001986552567237132 +/- 0.0005838928231828477</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.0014669926650366927 +/- 0.0015511708484657312</t>
+          <t>-0.0018031784841076371 +/- 0.0011713794557907677</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.0006112469437652646 +/- 0.0010674968946560491</t>
+          <t>-0.004003667481662654 +/- 0.0014167881401588374</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0029339853300733632 +/- 0.0010779457266838857</t>
+          <t>0.001039119804400923 +/- 0.000614295575863138</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0025366748166259167 +/- 0.001478724988191081</t>
+          <t>-0.0028728606356969054 +/- 0.002096140366684852</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.0044621026894865355 +/- 0.0017620458808556964</t>
+          <t>-0.006295843520782452 +/- 0.0017027369532009928</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0069987775061124856 +/- 0.001328319915165092</t>
+          <t>-0.0031173594132029915 +/- 0.0010657454629683708</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.010207823960880213 +/- 0.0010865763346351478</t>
+          <t>-0.0019254278728607077 +/- 0.0016290046419604573</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.000519559902200506 +/- 0.0005302369062621643</t>
+          <t>0.00012224938875300407 +/- 0.0004773991244441815</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.0032090464547677388 +/- 0.0012545461950961901</t>
+          <t>-0.0009168704156479856 +/- 0.0010409160370370913</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.00195599022004892 +/- 0.0013475188071545847</t>
+          <t>0.0025366748166258503 +/- 0.0014596520704473807</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0001833740831295949 +/- 0.0013544327509877993</t>
+          <t>-0.0017114914425428785 +/- 0.0008983458714363813</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0017420537897310684 +/- 0.0013464786535397858</t>
+          <t>-0.0002750611246944312 +/- 0.0016820400862857076</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.0007029339853301009 +/- 0.0009572408168316782</t>
+          <t>-0.0005195599022005615 +/- 0.000307147787931574</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.0002750611246943757 +/- 0.0002538699224608072</t>
+          <t>-0.00033618581907096656 +/- 0.0005195599022004903</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.00012224938875305958 +/- 0.00028010853881149536</t>
+          <t>0.00012224938875302627 +/- 0.0002444987775060942</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.009413202933985333 +/- 0.0015750731939761667</t>
+          <t>-0.0032090464547678056 +/- 0.001368497137972989</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.0025061124694376715 +/- 0.0013237413097621031</t>
+          <t>0.0046454767726160865 +/- 0.0008403256164344465</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.0013447432762836442 +/- 0.0007128303049933344</t>
+          <t>0.00015281173594128283 +/- 0.0007640586797066095</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.0057457212713936555 +/- 0.0013024007183778967</t>
+          <t>-0.0020782396088020127 +/- 0.001182095330428712</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.005073349633251867 +/- 0.0014542025982115354</t>
+          <t>-0.0007029339853301453 +/- 0.0009765614491852618</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.00015281173594131615 +/- 0.0007881293984246872</t>
+          <t>-0.0008863080684597291 +/- 0.0009214433637947147</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.0025672371638142065 +/- 0.0009489104337567264</t>
+          <t>-3.0562347188334285e-05 +/- 0.0015369548851687335</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.003270171149144285 +/- 0.0013941925095302206</t>
+          <t>-0.002811735941320359 +/- 0.000983708859378433</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.00262836185819072 +/- 0.0015293393646939894</t>
+          <t>0.0028728606356967614 +/- 0.0014477651934385084</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.0018948655256723623 +/- 0.0010025195273139882</t>
+          <t>-0.002414425427872935 +/- 0.0012410721579612935</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.00012224938875305958 +/- 0.00034032789503852417</t>
+          <t>-0.00012224938875308178 +/- 0.00024449877750612193</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.0014058679706601574 +/- 0.0009489104337567063</t>
+          <t>-0.001283618581907131 +/- 0.0016784266769860777</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.001436430317848425 +/- 0.0011108057362705555</t>
+          <t>-0.0016809290953545774 +/- 0.0013547775219622006</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.0010391198044009565 +/- 0.00045741532845646084</t>
+          <t>0.0001833740831295283 +/- 0.0003667481662591676</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.0020476772616136673 +/- 0.0014075279877346467</t>
+          <t>-0.001466992665036726 +/- 0.0014516310619850665</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.0022310513447433068 +/- 0.000773776827700015</t>
+          <t>0.0006723716381417666 +/- 0.0010209836851155479</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.002842298288508549 +/- 0.0016853686649098273</t>
+          <t>-6.661338147750939e-17 +/- 0.0013038342914243053</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.00018337408312958382 +/- 0.00031167600938831834</t>
+          <t>-3.0562347188278774e-05 +/- 0.00016458327650166254</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-0.0006112469437652756 +/- 0.0006695874786126705</t>
+          <t>-0.0003056234718826767 +/- 0.0004533128659594087</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.0002750611246943868 +/- 0.0004418347278362044</t>
+          <t>-0.00036674816625922315 +/- 0.0003564151524966776</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.0004278728606356919 +/- 0.0007258155309925533</t>
+          <t>-0.001039119804401034 +/- 0.00045741532845648453</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.0030562347188264226 +/- 0.0019183807856326834</t>
+          <t>0.0013141809290953099 +/- 0.0012604884246516723</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.00015281173594132723 +/- 0.00031317086693032634</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0022310513447432955 +/- 0.001427297607437142</t>
+          <t>0.0006418092909534989 +/- 0.0012854364819568185</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.00195599022004892 +/- 0.0017027369532009937</t>
+          <t>0.0014058679706601019 +/- 0.0011204341552459361</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.00018337408312960602 +/- 0.0002027276766721144</t>
+          <t>-0.00024449877750614134 +/- 0.0002664363657421264</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.002169926650366727 +/- 0.0009112500926574513</t>
+          <t>-0.0011613691931540936 +/- 0.0008941771906068311</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.0021393643031784927 +/- 0.0014335011490902703</t>
+          <t>-0.0015281173594132724 +/- 0.0017016394751925472</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0003667481662591787 +/- 0.0010209836851155325</t>
+          <t>-0.0008557457212714503 +/- 0.00032916655300332096</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.005308168681804814 +/- 0.0011421360501938916</t>
+          <t>0.014656443526983198 +/- 0.0018512941451748295</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.008021232674727286 +/- 0.0014006891285211428</t>
+          <t>0.002447655558832207 +/- 0.0020687065652958423</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.0015924506045414844 +/- 0.0024289307321703145</t>
+          <t>-0.0012680625184311456 +/- 0.0016736612944456353</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.004570923031554153 +/- 0.0011887728912265657</t>
+          <t>0.001120613388381031 +/- 0.001200058386869695</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0027720436449424346 +/- 0.001828369212621644</t>
+          <t>-0.0055735771158949895 +/- 0.0016230124335968115</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.012739604836331408 +/- 0.0018073197813086978</t>
+          <t>0.004511943379534078 +/- 0.0017647141610589586</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0002654084340902085 +/- 0.0002782064621662286</t>
+          <t>2.2204460492503132e-17 +/- 0.00026376502241222795</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.007991742848717232 +/- 0.001534888077814578</t>
+          <t>-0.0007372456502506397 +/- 0.0008470307647505168</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.014479504570922975 +/- 0.0029296030878303535</t>
+          <t>0.026806251843114137 +/- 0.003742885149450788</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.022884104983780552 +/- 0.002381931053530949</t>
+          <t>0.026245945148923623 +/- 0.002467295861203397</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.009761132409318852 +/- 0.0012817053265762684</t>
+          <t>-0.0070480684163963135 +/- 0.0015405435430974985</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.014125626658802782 +/- 0.001500507724353702</t>
+          <t>-0.005927455028015316 +/- 0.0017065923086087029</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.00014744913005019234 +/- 0.0014522055148623013</t>
+          <t>0.008699498672957839 +/- 0.0021397912042078137</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.0193748156885874 +/- 0.0012857699414090917</t>
+          <t>0.01745797699793573 +/- 0.001330641601023691</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.003715718077263397 +/- 0.002489053122501828</t>
+          <t>-0.010203479799469173 +/- 0.0013332532651674754</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.003568268947213149 +/- 0.0020703874159207405</t>
+          <t>0.00457092303155412 +/- 0.00124592333673122</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0033618401651429597 +/- 0.0011587663051836196</t>
+          <t>0.003627248599233268 +/- 0.0011194487110647296</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.0035092892951932076 +/- 0.0010911235623709513</t>
+          <t>-0.0018873488646416804 +/- 0.0013397601523563278</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.00607490415806553 +/- 0.0010401174926893814</t>
+          <t>-0.001061633736360923 +/- 0.0013135392185974668</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00020642878207017824 +/- 0.0002654084340902344</t>
+          <t>-0.00017693895606013532 +/- 0.00027027871984404813</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0028900029489825176 +/- 0.0017879689048922556</t>
+          <t>0.00940725449719848 +/- 0.0016912357368256818</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.01135358301386028 +/- 0.0011666199023799746</t>
+          <t>0.0005603066941905155 +/- 0.0018484734820660383</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-0.005013270421704563 +/- 0.0015548718757256448</t>
+          <t>0.003951636685343563 +/- 0.0013590939099737975</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0003243880861102277 +/- 0.0018056348587250487</t>
+          <t>0.0027720436449425122 +/- 0.001252536749135686</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0016219404305514162 +/- 0.0012598059193921392</t>
+          <t>-0.0005308168681804393 +/- 0.0008423979272831331</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0006782659982306871 +/- 0.0004943395639705198</t>
+          <t>-0.00032438808611026106 +/- 0.000955124431772417</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.006812149808316193 +/- 0.0022476200545315716</t>
+          <t>0.006281332940135653 +/- 0.002249940378674427</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.013712769094662392 +/- 0.0022235015919957832</t>
+          <t>0.005986434680035413 +/- 0.0017398997345915552</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.005986434680035435 +/- 0.001965226432503246</t>
+          <t>0.0033618401651430265 +/- 0.0007824535040649718</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.01828369212621652 +/- 0.002130627174071186</t>
+          <t>-0.005308168681804759 +/- 0.0014744913005013105</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.0005603066941905488 +/- 0.0006248782099798758</t>
+          <t>-0.000471837216160409 +/- 0.0004969713814907768</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.0007372456502506397 +/- 0.00046158878922142245</t>
+          <t>-0.0012385726924210804 +/- 0.00031761514639542</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,272 +1491,272 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.01182542023002069 +/- 0.0012047595526874474</t>
+          <t>-0.001061633736360923 +/- 0.000866820315936247</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.008728988498967916 +/- 0.001974717669452467</t>
+          <t>0.0028605131229725634 +/- 0.0012018687037637485</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>8.8469478030051e-05 +/- 0.00035017228213030127</t>
+          <t>0.0004718372161604534 +/- 0.0005927381669785092</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-5.8979652020096916e-05 +/- 0.00036832780881146377</t>
+          <t>-0.00035387791212028176 +/- 0.0005868401280487099</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0009731642583308165 +/- 0.0011425166987797514</t>
+          <t>0.0015334709525213984 +/- 0.001479202147329321</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.00905337658507821 +/- 0.0011271904956423509</t>
+          <t>0.003686228251253321 +/- 0.001217683445712933</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.0005013270421704852 +/- 0.0007229519712256898</t>
+          <t>-0.0012680625184311345 +/- 0.000813513077212281</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.0010911235623709214 +/- 0.0015607335443703066</t>
+          <t>0.005897965202005318 +/- 0.0016205994295528268</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.01067531701562966 +/- 0.0015649070081299628</t>
+          <t>-0.001061633736360934 +/- 0.0007598996594942694</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.0017693895606016418 +/- 0.0016419240232468325</t>
+          <t>-0.00011795930404007171 +/- 0.0013969589244856408</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.011972869360070837 +/- 0.0018472969346347314</t>
+          <t>0.0069006192863462325 +/- 0.001409354543833477</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.004128575641403775 +/- 0.0014626478050884276</t>
+          <t>0.001120613388381042 +/- 0.0007437051142977414</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2.948982600996519e-05 +/- 0.0012403267970989853</t>
+          <t>0.005956944854025381 +/- 0.0009939427629815675</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.007962253022707222 +/- 0.0016098312077801622</t>
+          <t>0.00690061928634621 +/- 0.00121016128155015</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.00035387791212029287 +/- 0.00045303130332462107</t>
+          <t>-0.00041285756414032314 +/- 0.00042119896364157237</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.0029489826010027143 +/- 0.001038443931681454</t>
+          <t>0.0005897965202005473 +/- 0.0008129783988257204</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.0029489826010027143 +/- 0.0013449429962832592</t>
+          <t>0.007431436154526683 +/- 0.0011096955306532873</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.025951046888823416 +/- 0.0015660180533590997</t>
+          <t>-0.0036567384252432665 +/- 0.0011662471208071326</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.018106753170156344 +/- 0.002428930732170341</t>
+          <t>-0.007166027720436419 +/- 0.0013581337587342394</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.0015924506045414844 +/- 0.001128347181935071</t>
+          <t>0.0003833677381303691 +/- 0.00037418394398258545</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-0.0010616337363610006 +/- 0.000988679127941033</t>
+          <t>-0.0001474491300500924 +/- 0.0005934713004275533</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.00014744913005017014 +/- 0.0004615887892214331</t>
+          <t>-0.0009731642583308275 +/- 0.00043839778081152696</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.023916248894131565 +/- 0.003037452079032728</t>
+          <t>-0.005013270421704496 +/- 0.0017093927155635098</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.012061338838100899 +/- 0.0019040930058812006</t>
+          <t>0.013476850486582159 +/- 0.0018976880617158477</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>1.1102230246251566e-17 +/- 0.0001318825112061202</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-0.0008257151282807018 +/- 0.00031761514639542</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.0017693895606015974 +/- 0.0010714185859383469</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.005249189029784751 +/- 0.0009491876696804035</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.0024181657328221752 +/- 0.0005564129243324431</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.0074019463285166735 +/- 0.0011379405120362353</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-0.0018873488646416914 +/- 0.0012455742897046816</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.00616337363609557 +/- 0.0013922821154954757</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.0023591860808021225 +/- 0.0008340982379080515</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.00011795930404012722 +/- 0.0003538779121203169</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.004541433205544088 +/- 0.0011587663051836371</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.003420819817163079 +/- 0.0012800079277033695</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>-0.0001769389560601242 +/- 0.0004413633013003707</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.021675022117369526 +/- 0.001556269513648941</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.002801533470952522 +/- 0.0013005648523267334</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.010409908581539395 +/- 0.0013581337587342374</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>8.846947803009542e-05 +/- 0.0002303229040373519</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>-0.000678265998230565 +/- 0.0004764227195931568</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.00029489826010029583 +/- 0.0005595301079625507</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-0.00044234739015046597 +/- 0.0005477492073431877</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>-0.0023296962547921574 +/- 0.0012119565076988558</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-0.012916543792391688 +/- 0.0016619289653323787</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.0015039811265113224 +/- 0.0007396010736646619</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-0.01618991447950463 +/- 0.001268062518431152</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-0.010704806841639691 +/- 0.00195635603546117</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-0.007549395458566854 +/- 0.0017947654443766447</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.0007962253022706812 +/- 0.001165128060462299</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>-0.0012385726924211804 +/- 0.00022068165065018013</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>-0.0015924506045414844 +/- 0.001252536749135679</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>-0.007166027720436519 +/- 0.0013772096052887762</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-0.004099085815393732 +/- 0.000796225302270714</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.005514597463874893 +/- 0.0011946109761444557</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>-0.0029194927749926825 +/- 0.0010750649444740735</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.013270421704511903 +/- 0.0006852816301163065</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.00047183721616038675 +/- 0.00019561337601625448</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>-0.004806841639634352 +/- 0.000685915856656612</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>-0.002831023296962598 +/- 0.0007247540977554878</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-0.00014744913005010352 +/- 0.0005477492073431757</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>-0.0029194927749926157 +/- 0.0012403267970989866</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.00038336773813031356 +/- 0.0004578052107419728</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.0017693895606015531 +/- 0.0009869183444813567</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>-0.00020642878207021153 +/- 0.00029636908348928997</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0015039811265113111 +/- 0.000501327042170448</t>
+          <t>0.00035387791212033727 +/- 0.0003439075137036378</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.0011206133883810642 +/- 0.0005868401280487243</t>
+          <t>-0.0018283692126216389 +/- 0.0007437051142977721</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.01049837805956948 +/- 0.0008567289322520975</t>
+          <t>0.005072250073724582 +/- 0.0016514302565614836</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.005278678855794805 +/- 0.0010669450023666122</t>
+          <t>0.0010321439103509467 +/- 0.0006359144397772905</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.002034797994691784 +/- 0.001058762788028062</t>
+          <t>0.002683574166912406 +/- 0.0012047595526874305</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.001179593040401028 +/- 0.0011268046696869954</t>
+          <t>0.012887053966381623 +/- 0.0012857699414091273</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.00333235033913305 +/- 0.0006467623768641032</t>
+          <t>-0.00023591860808017673 +/- 0.000615765644878241</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.00210121337673872 +/- 0.001293048373776489</t>
+          <t>-0.0006510802012429595 +/- 0.0008028801400562469</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.015951464930452762 +/- 0.0019695392875969096</t>
+          <t>-0.004054453980467587 +/- 0.0013565157308512551</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0018052678307191705 +/- 0.0017580759680709455</t>
+          <t>0.0019236460491269703 +/- 0.0017116299190199917</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0016572950577093959 +/- 0.0019325040209901858</t>
+          <t>0.001509322284699599 +/- 0.0012998041583899193</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.0034921574430304527 +/- 0.0017894307733448973</t>
+          <t>0.00020716188221366893 +/- 0.0018672733417398517</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.001538916839301585 +/- 0.0016990470665176041</t>
+          <t>0.0026635099141758102 +/- 0.0017608138242845408</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.00032554010062147977 +/- 0.0005684928296033796</t>
+          <t>-5.918910920390541e-05 +/- 0.00017756732761171621</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.011453092630955886 +/- 0.001642697731444574</t>
+          <t>0.00041432376442733786 +/- 0.0014328166246712027</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.015418762947617659 +/- 0.0027267170578307003</t>
+          <t>0.020834566439775083 +/- 0.0038522971518847194</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.007842556969517633 +/- 0.002543238316501213</t>
+          <t>0.013051198579461399 +/- 0.0033284336538003945</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.007013909440662924 +/- 0.0009819863878684438</t>
+          <t>0.006510802012429706 +/- 0.0006207806144836534</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0013021604024859635 +/- 0.0012708440694634018</t>
+          <t>0.0012429712932820248 +/- 0.0016035770564242664</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.002989050014797312 +/- 0.0020394492043823635</t>
+          <t>0.0023083752589523666 +/- 0.0015592707750600285</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.016454572358686026 +/- 0.001946052941435154</t>
+          <t>0.015182006510802027 +/- 0.0013370058594941333</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.00834566439775084 +/- 0.0024108211724671626</t>
+          <t>0.010802012429712949 +/- 0.002536341386335111</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.002693104468777707 +/- 0.0009855475469278958</t>
+          <t>0.000917431192660556 +/- 0.0019471777626038453</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.001805267830719115 +/- 0.001062522821604967</t>
+          <t>0.0028114826871855625 +/- 0.001510482409609353</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.0006510802012429595 +/- 0.001268084361386692</t>
+          <t>-0.00017756732761171624 +/- 0.0009833233338760491</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.0007990529742527231 +/- 0.0013693678959762136</t>
+          <t>0.0026339153595738352 +/- 0.000640911743939295</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.00041432376442733786 +/- 0.00042269478712889737</t>
+          <t>0.0005918910920390541 +/- 0.0004185302049047261</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.007369044095886346 +/- 0.0015740853680937781</t>
+          <t>0.004084048535069551 +/- 0.0021739411272218997</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0008582420834566395 +/- 0.0010949985202722715</t>
+          <t>-0.0018348623853210676 +/- 0.0008349651364111056</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.0010654039656702973 +/- 0.001344518104954169</t>
+          <t>0.0013613495116898467 +/- 0.001872659605748011</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.003018644569399276 +/- 0.0011673917089858514</t>
+          <t>0.0006510802012429706 +/- 0.0015020512033677954</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.0025451316957679658 +/- 0.00240500143875821</t>
+          <t>-0.0005918910920390541 +/- 0.0011073268383468109</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.00026635099141757433 +/- 0.0006544345779075343</t>
+          <t>0.000503107428233196 +/- 0.0005776626604303872</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.007694584196507803 +/- 0.002988903503510527</t>
+          <t>-0.00017756732761171624 +/- 0.002915326512228398</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.0019236460491269258 +/- 0.0013448437724180595</t>
+          <t>-8.878366380585812e-05 +/- 0.0011541876294761555</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.005179047055341834 +/- 0.0009657986902681518</t>
+          <t>0.0071026931044687715 +/- 0.0011308063435657204</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.007132287659070735 +/- 0.001251748208496998</t>
+          <t>0.0034329683338266024 +/- 0.0005327019828351808</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.00017756732761171624 +/- 0.0005799324635177588</t>
+          <t>0.00038472920982538514 +/- 0.00039815401145526687</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.0010654039656702973 +/- 0.0003789952197355864</t>
+          <t>0.0007694584196507703 +/- 0.0006643961030080865</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.008256880733944972 +/- 0.0010788828726581</t>
+          <t>0.003255401006214853 +/- 0.0010588069736607712</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.9594554601952706e-05 +/- 0.0010118568213837496</t>
+          <t>-0.00011837821840781082 +/- 0.0008391504515393648</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.0018052678307191705 +/- 0.0009020272657075303</t>
+          <t>-0.00014797277300976353 +/- 0.0003308771792689774</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.00017756732761171624 +/- 0.0010849542929756157</t>
+          <t>0.0009470257472624866 +/- 0.0004916616669380246</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.003048239124001173 +/- 0.0020463088384803305</t>
+          <t>-0.0021899970405445334 +/- 0.001510192461932312</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.0018052678307191928 +/- 0.001956153047607081</t>
+          <t>0.00257472625036993 +/- 0.0010837427300148595</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.0005327019828351487 +/- 0.0008658620206171961</t>
+          <t>-0.00011837821840781082 +/- 0.0007625983265300321</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.0029594554601952926 +/- 0.0016424311246536363</t>
+          <t>0.00109499852027225 +/- 0.0008683871412323732</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.00014797277300976353 +/- 0.0010772580481326409</t>
+          <t>0.0006510802012429595 +/- 0.001006214856466392</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.0028706717963894344 +/- 0.0013821005538722344</t>
+          <t>0.004735128736312544 +/- 0.0010251854439590684</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.0016572950577093625 +/- 0.001611205396722835</t>
+          <t>0.008552826279964499 +/- 0.0014404372327479315</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.002426753477360144 +/- 0.0016520018629124424</t>
+          <t>8.878366380584701e-05 +/- 0.002281085607877236</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-0.0031666173424089615 +/- 0.0013038408269849505</t>
+          <t>-0.004350399526487125 +/- 0.0014380030320516734</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.00029594554601952705 +/- 0.0010079542092883156</t>
+          <t>-0.0034033737792246166 +/- 0.0007398638650488687</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.00029594554601952705 +/- 0.0006483842053923128</t>
+          <t>0.000710269310446865 +/- 0.0005948431856241911</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.006303640130216048 +/- 0.0012971060669316992</t>
+          <t>0.000917431192660545 +/- 0.0012305784484339583</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.002870671796389501 +/- 0.0014621626903859885</t>
+          <t>-0.00014797277300976353 +/- 0.0017867367680524779</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0036401302160402826 +/- 0.0011767324860651716</t>
+          <t>-0.0007398638650488176 +/- 0.0010690968847699388</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.008079313406333267 +/- 0.001515114026181753</t>
+          <t>0.006836342113051208 +/- 0.0020608097494588533</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-0.001390944066291777 +/- 0.0007133454154006352</t>
+          <t>0.0017460787215152207 +/- 0.00079905297425274</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0009766203018644394 +/- 0.0007492742764825057</t>
+          <t>0.0024859425865640826 +/- 0.0006902576969334782</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00029594554601952705</t>
+          <t>-8.878366380585812e-05 +/- 0.0003514158652571087</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.00544539804675942 +/- 0.0010929970590482121</t>
+          <t>0.010091743119266073 +/- 0.0017828109478341574</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.00292986090559334 +/- 0.0014465048132406048</t>
+          <t>0.0017756732761171844 +/- 0.001565996632769809</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0006065078878934249</t>
+          <t>-8.878366380585812e-05 +/- 0.0004781146617757686</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-0.0015389168393015406 +/- 0.001268084361386692</t>
+          <t>-0.0032258064516129 +/- 0.001179705914649021</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.0033441846700207447 +/- 0.0016319994884832398</t>
+          <t>0.0031962118970109477 +/- 0.0017697444673247856</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>-0.0005622965374371014 +/- 0.0006934225814655086</t>
+          <t>0.00142053862089373 +/- 0.0007463462688912852</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.002693104468777796 +/- 0.0006934225814655329</t>
+          <t>0.0024267534773601664 +/- 0.0014118804903079899</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.0033737792246226416 +/- 0.0012639335012762905</t>
+          <t>0.0008878366380586034 +/- 0.0017855108764721409</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.0004439183190293128 +/- 0.0012003136898889306</t>
+          <t>-0.000917431192660545 +/- 0.00148238884715811</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.001006214856466403 +/- 0.0006374862157010484</t>
+          <t>-0.0009174311926605338 +/- 0.0007059402451539714</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-0.00032554010062147977 +/- 0.00027919446972644076</t>
+          <t>5.918910920390541e-05 +/- 0.0002899662317588794</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-0.001686889612311304 +/- 0.0013565157308512144</t>
+          <t>0.0008878366380585922 +/- 0.0013690480622930228</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.0006806747558449122 +/- 0.0010170370096146358</t>
+          <t>-0.00020716188221366893 +/- 0.0008164021440741918</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.00038472920982538514 +/- 0.0005302300345418346</t>
+          <t>-0.000503107428233196 +/- 0.0005622965374371014</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.0009766203018644725 +/- 0.0019090208254359544</t>
+          <t>-0.0019828351583308424 +/- 0.0014196134898149038</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.002604320804971927 +/- 0.0012680843613867324</t>
+          <t>0.0012725658478839775 +/- 0.0013947169775611907</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-0.0012429712932820135 +/- 0.0014546559014435379</t>
+          <t>-0.0014797277300976353 +/- 0.0010833385745914646</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-0.00014797277300976353 +/- 0.0002728483118464848</t>
+          <t>-5.918910920390541e-05 +/- 0.00017756732761171621</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.0017164841669132902 +/- 0.000491661666938062</t>
+          <t>-0.00026635099141757433 +/- 0.0005367966009830343</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.002278780704350358 +/- 0.0009456374849760383</t>
+          <t>0.0009766203018644394 +/- 0.0004781146617757686</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.000503107428233196 +/- 0.0006624157823497777</t>
+          <t>0.0 +/- 0.0004584768684471556</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.0021012133767387086 +/- 0.0011419817331503543</t>
+          <t>0.000503107428233196 +/- 0.0013693678959762138</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>-0.0005622965374371014 +/- 0.00044784687630722937</t>
+          <t>-0.00032554010062147977 +/- 0.00030897622103907553</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>-0.00272269902337966 +/- 0.0013994188123748789</t>
+          <t>0.001213376738680072 +/- 0.0008823942891906289</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.0026339153595738795 +/- 0.00146455673650887</t>
+          <t>0.00014797277300976353 +/- 0.001060872940451885</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>-0.0009470257472624866 +/- 0.0004916616669380246</t>
+          <t>-0.00029594554601952705 +/- 0.00035016749234090017</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.0006510802012429818 +/- 0.0013021604024859507</t>
+          <t>0.000710269310446865 +/- 0.0012777172622031672</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>-0.003936075762059743 +/- 0.0015266315923680434</t>
+          <t>-8.878366380584701e-05 +/- 0.0015606743857277483</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.0017460787215152096 +/- 0.0008520970730327143</t>
+          <t>-0.0014797277300976353 +/- 0.0008779163642610865</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.001683899556868529 +/- 0.0005766387384325859</t>
+          <t>-0.0030428360413589208 +/- 0.0010407039854539702</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.004283604135893626 +/- 0.001130733188124345</t>
+          <t>-0.0005908419497784312 +/- 0.0008663443603317639</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0016248153618907302 +/- 0.0009549914254207031</t>
+          <t>-0.003692762186115195 +/- 0.0004624069672820811</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.004313146233382659 +/- 0.0013615029390608984</t>
+          <t>-0.00017725258493352935 +/- 0.0010250724710722235</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.0024224519940915677 +/- 0.0009869006256124065</t>
+          <t>0.0007976366322008821 +/- 0.0009346701340949064</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0013293943870015036 +/- 0.001168687766313322</t>
+          <t>-0.0022451994091580384 +/- 0.0010830311834459832</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0001477104874446078 +/- 0.000498728006385053</t>
+          <t>-0.0001477104874446078 +/- 0.00023817600438104895</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.0047267355982274495 +/- 0.0012740832291195103</t>
+          <t>-0.0030723781388478423 +/- 0.0009360696908570032</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.02688330871491883 +/- 0.0020889417464890732</t>
+          <t>0.024992614475627783 +/- 0.0032769098077074536</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.020029542097488938 +/- 0.002351521269380495</t>
+          <t>0.025612998522895114 +/- 0.0019731379000882264</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.0015361890694239211 +/- 0.0006965923853797067</t>
+          <t>-0.005376661742983724 +/- 0.001119485691078069</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.0009453471196454899 +/- 0.0006965923853797067</t>
+          <t>-0.0019497784342688228 +/- 0.001788212224569746</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0054062038404727565 +/- 0.0013280807558634508</t>
+          <t>-0.0029246676514032345 +/- 0.001988119510592751</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.02035450516986702 +/- 0.002274741506647004</t>
+          <t>-0.008744460856720782 +/- 0.0016564662651552277</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.006440177252585011 +/- 0.001038605366691099</t>
+          <t>0.005819793205317558 +/- 0.0018117279889467773</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.005022156573116665 +/- 0.0009342031492373303</t>
+          <t>-0.003692762186115195 +/- 0.0011908800219052448</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.0002954209748892156 +/- 0.0009153284126930333</t>
+          <t>0.002688330871491862 +/- 0.0005826612385026859</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0014180206794682682 +/- 0.0014460547415681808</t>
+          <t>0.0015361890694239211 +/- 0.0008334851391235339</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.005819793205317547 +/- 0.000997893397580765</t>
+          <t>-0.0009158050221565684 +/- 0.0007754448891229908</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.0005022156573116666 +/- 0.0003748471946957003</t>
+          <t>0.0005022156573116666 +/- 0.0005125362355361117</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.005908419497784312 +/- 0.0015743471308093538</t>
+          <t>-0.0049335302806499 +/- 0.0013214930130779866</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.0019497784342688228 +/- 0.0007726261052066146</t>
+          <t>0.0037813884785819598 +/- 0.001119485691078069</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.004992614475627854 +/- 0.00141955849651213</t>
+          <t>0.0008271787296898036 +/- 0.001103783851832751</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0009453471196455232 +/- 0.0015339149170750356</t>
+          <t>0.0008271787296898036 +/- 0.000950870129360768</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00307237813884792 +/- 0.0017586855026454937</t>
+          <t>0.001683899556868529 +/- 0.0016129552371897935</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.00017725258493352935 +/- 0.0008480177308364696</t>
+          <t>-0.00023633677991137249 +/- 0.0005878803173451195</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.006292466765140403 +/- 0.0018308951766435552</t>
+          <t>0.0038109305760708812 +/- 0.0023165601087285367</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.0020974889217134306 +/- 0.0009926320600538467</t>
+          <t>0.0013884785819793133 +/- 0.001955365523589108</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.0016248153618906858 +/- 0.000738552437223039</t>
+          <t>0.0004135893648449018 +/- 0.0008683567773529685</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.0005022156573116666 +/- 0.0009891089537833453</t>
+          <t>0.0027178729689807833 +/- 0.001142633950121927</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-0.00023633677991137249 +/- 0.0006168571054009155</t>
+          <t>-0.0006203840472673528 +/- 0.0003840472673559803</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.954209748892156e-05 +/- 0.000245395091962128</t>
+          <t>-0.0001477104874446078 +/- 0.00033029069091577225</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0017134416543574838 +/- 0.0011116624946663168</t>
+          <t>-0.0004135893648449018 +/- 0.0006224906205525958</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.006587887740029508 +/- 0.0009158050221565683</t>
+          <t>-0.005819793205317547 +/- 0.0019010517628592124</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-0.0004431314623338234 +/- 0.000515930552335979</t>
+          <t>0.0006203840472673528 +/- 0.0004061366937922437</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.0008567208271787252 +/- 0.0007169666823935914</t>
+          <t>-0.0009158050221565684 +/- 0.0005826612385026859</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0036927621861152725 +/- 0.0015250705464272534</t>
+          <t>0.0012998522895125487 +/- 0.0016774085159915293</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.0009748892171344114 +/- 0.0008255946004420707</t>
+          <t>0.001152141802067941 +/- 0.0005974519473015237</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.00011816838995568624 +/- 0.0002707577958614958</t>
+          <t>-0.0009453471196454899 +/- 0.0007680945347119605</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.0013884785819793465 +/- 0.0013984993061796015</t>
+          <t>-5.908419497784312e-05 +/- 0.0012308813386114948</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.0031019202363367637 +/- 0.0008170940434823786</t>
+          <t>-0.0009748892171344114 +/- 0.0007595249708822673</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.0004135893648449018 +/- 0.0005317577548005881</t>
+          <t>-0.0012112259970457838 +/- 0.0005518919259163755</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.005553914327917364 +/- 0.0011502465189915322</t>
+          <t>-0.0030428360413589208 +/- 0.0012537131565094732</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-2.954209748892156e-05 +/- 0.00042708514903399956</t>
+          <t>0.0038109305760708812 +/- 0.0019482111779967459</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.002658788774003018 +/- 0.0010402846003934778</t>
+          <t>0.0017134416543574504 +/- 0.0006025429262738858</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0021861152141802844 +/- 0.000737961358747261</t>
+          <t>0.0004431314623338234 +/- 0.0014059679804184024</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.0003840472673559803 +/- 0.0004772671911788309</t>
+          <t>-2.954209748892156e-05 +/- 0.00030842855270045774</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.000531757754800588 +/- 0.00047267355982274497</t>
+          <t>0.0023633677991137247 +/- 0.0007816104316291216</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0015657311669128981 +/- 0.0010655650692391193</t>
+          <t>-0.010162481536189016 +/- 0.0013092183046475758</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.002540620384047343 +/- 0.000858247506430397</t>
+          <t>-0.002304283604135882 +/- 0.0008643272578037057</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.003692762186115284 +/- 0.0015078050404933616</t>
+          <t>0.0015066469719349994 +/- 0.0011996419795714532</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.001004431314623333 +/- 0.0004219455496923375</t>
+          <t>0.0002067946824224509 +/- 0.0005125362355361117</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.00047267355982274497 +/- 0.0004007285071270448</t>
+          <t>0.000265878877400294 +/- 0.00046616643539318815</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-2.954209748892156e-05 +/- 8.862629246676468e-05</t>
+          <t>-8.862629246676468e-05 +/- 0.00018916172045591774</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.005228951255539227 +/- 0.0013605410859284365</t>
+          <t>-0.0013884785819793133 +/- 0.0009062252082822977</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.0029246676514032345 +/- 0.0017943024684266037</t>
+          <t>0.001063515509601176 +/- 0.0013092183046475758</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.0007976366322008821 +/- 0.0003748471946957003</t>
+          <t>0.0004135893648449018 +/- 0.000442145629160877</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0029542097488922557 +/- 0.0007816104316291469</t>
+          <t>0.00360413589364843 +/- 0.0011037838518327507</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.0007976366322009043 +/- 0.0015296417685081022</t>
+          <t>0.0011816838995568624 +/- 0.0009248139345641622</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0003249630723781372 +/- 0.0003355337279645639</t>
+          <t>-0.00011816838995568624 +/- 0.00019596010578170652</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.0020974889217134974 +/- 0.0003606072560039971</t>
+          <t>0.004017725258493332 +/- 0.0008582475064303619</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.0011225997045790082 +/- 0.0014877020161907601</t>
+          <t>0.0006794682422451958 +/- 0.0014047259589918674</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.0007680945347119716 +/- 0.0011147983612474757</t>
+          <t>-0.0006203840472673528 +/- 0.0011776148554206584</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.002333825701624881 +/- 0.0008505867089446653</t>
+          <t>-0.0033087149187592145 +/- 0.0005728425237714982</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>2.954209748892156e-05 +/- 0.00024539509196212794</t>
+          <t>0.0004135893648449018 +/- 0.0002707577958614958</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.0002954209748892267 +/- 0.0013666213892136508</t>
+          <t>-0.002747415066469705 +/- 0.001167193280067256</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.0031905465288035286 +/- 0.0009508701293607679</t>
+          <t>0.0004431314623338234 +/- 0.0013424600020681481</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.000531757754800588 +/- 0.000490790183924256</t>
+          <t>0.0006499261447562743 +/- 0.0005573991806237255</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.0027769571639586267 +/- 0.0010667929149345758</t>
+          <t>-0.009364844903988135 +/- 0.0015466635288281661</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.004372230428360502 +/- 0.0008743662385198621</t>
+          <t>0.0011816838995568624 +/- 0.0007473625193898642</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.0002954209748892156 +/- 0.0007114679219375027</t>
+          <t>-0.0031610044313146067 +/- 0.000747946168459208</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>8.862629246676468e-05 +/- 0.0001353788979307479</t>
+          <t>-0.00011816838995568624 +/- 0.00023633677991137249</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-5.908419497784312e-05 +/- 0.00041358936484490186</t>
+          <t>0.000531757754800588 +/- 0.000368980679373611</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0002067946824224509 +/- 0.00018916172045591774</t>
+          <t>0.0 +/- 0.00039634882909892665</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-2.954209748892156e-05 +/- 0.0003355337279645639</t>
+          <t>-0.0009748892171344114 +/- 0.0006871316602430101</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.002245199409158105 +/- 0.0008882302143795372</t>
+          <t>-0.0027769571639586267 +/- 0.0013356164910436933</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.908419497784312e-05 +/- 0.00011816838995568624</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-0.000265878877400294 +/- 0.0005022156573116664</t>
+          <t>-0.000265878877400294 +/- 0.00015908906372627698</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.0019202363367799014 +/- 0.000579657810054608</t>
+          <t>-0.0014180206794682348 +/- 0.0010635155096011763</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-0.001004431314623333 +/- 0.0005636272977352678</t>
+          <t>-0.0012998522895125487 +/- 0.000737961358747222</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>-0.0005022156573116666 +/- 0.00026587887740029407</t>
+          <t>0.0001477104874446078 +/- 0.00023817600438104898</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0022156573116691946 +/- 0.0011151897245599703</t>
+          <t>-0.0009453471196454899 +/- 0.001516750091934224</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.0009158050221565684 +/- 0.0007754448891229908</t>
+          <t>-0.00227474150664696 +/- 0.00063429573274989</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.0004431314623338345 +/- 0.0009365357450013389</t>
+          <t>-0.0006499261447562743 +/- 0.0008014570142540895</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8.88099467140524e-05 +/- 0.0014625955390214</t>
+          <t>-0.007400828892835998 +/- 0.0012629206043636356</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.003433984606275864 +/- 0.0012003040220671028</t>
+          <t>-0.004884547069271761 +/- 0.002470591342061157</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0003256364712848181 +/- 0.0007992895204262935</t>
+          <t>-0.0006808762581409278 +/- 0.0018865001736358513</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0013617525162818334 +/- 0.0008998628865346644</t>
+          <t>0.0031675547661338065 +/- 0.0011845026064974838</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.002575488454706909 +/- 0.0005778336677306962</t>
+          <t>-0.008792184724689168 +/- 0.0008786750787244378</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.004440497335701621 +/- 0.0019139407785961702</t>
+          <t>-0.003315571343990531 +/- 0.002125674727177757</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.88099467140746e-05 +/- 0.0006356101407218285</t>
+          <t>0.0006216696269982335 +/- 0.000427970168584985</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.008288928359976277 +/- 0.0019457284458442694</t>
+          <t>-0.008940201302545903 +/- 0.001620359050728709</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.008644168146832476 +/- 0.0022263582802798157</t>
+          <t>0.002989934872705735 +/- 0.0021529162623536474</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.016607460035524012 +/- 0.002721090648620011</t>
+          <t>-0.0029603315571344103 +/- 0.0020121545847207227</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.004233274126702158 +/- 0.0019459536328649812</t>
+          <t>-0.004174067495559508 +/- 0.0020097577350495885</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0009769094138543765 +/- 0.001369773274275822</t>
+          <t>0.0006216696269982335 +/- 0.0015856437822193209</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.001568975725281263 +/- 0.0009733145188142902</t>
+          <t>-0.0033747779751332253 +/- 0.002331719202784501</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.0070159857904085075 +/- 0.0039318953904672145</t>
+          <t>-0.0108940201302546 +/- 0.003986677529788623</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.0056542332741267185 +/- 0.0019745655589878427</t>
+          <t>0.008200118413262281 +/- 0.002250825566047415</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-0.002989934872705724 +/- 0.001446933026625228</t>
+          <t>0.0002664298401420795 +/- 0.001410124969072189</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.0009177027827116269 +/- 0.0008925289183944087</t>
+          <t>-0.006631142687981073 +/- 0.0015279440971656404</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.00671995263469507 +/- 0.0013951298600293847</t>
+          <t>-0.011930136175251637 +/- 0.0022702095405610166</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.00219064535227943 +/- 0.0011480591728635482</t>
+          <t>-0.00248667850799289 +/- 0.0008900708335330389</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.0002664298401421239 +/- 0.00027927712054635895</t>
+          <t>-0.0002664298401421239 +/- 0.000279277120546406</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.01021314387211365 +/- 0.0012079458711132887</t>
+          <t>-0.0060982830076968695 +/- 0.001982317234195756</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.010005920663114265 +/- 0.0018992320819828721</t>
+          <t>-0.008792184724689178 +/- 0.0009551371110066071</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.002960331557134421 +/- 0.0009728642229221364</t>
+          <t>0.003907637655417384 +/- 0.00129580039243573</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0017169923031379875 +/- 0.000915312305135602</t>
+          <t>0.0032859680284191618 +/- 0.0016873889875666217</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0035227945529899716 +/- 0.0010462165214370712</t>
+          <t>0.00633510953226758 +/- 0.0016493058942787552</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0010065127294257015 +/- 0.00023682652457075737</t>
+          <t>-0.000355239786856143 +/- 0.00041444641799883087</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.011574896388395529 +/- 0.0020528997569669296</t>
+          <t>0.011752516281823566 +/- 0.002532943824823238</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.03013617525162817 +/- 0.0035789416837672893</t>
+          <t>-0.023268206039076388 +/- 0.0032863680488757624</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.003937240970988765 +/- 0.0014505624629958442</t>
+          <t>-0.00988750740082891 +/- 0.001383460206695993</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.004055654233274153 +/- 0.0015834315121747993</t>
+          <t>-0.005654233274126707 +/- 0.0015350967628731905</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.000740082889283633 +/- 0.00040264862370442553</t>
+          <t>5.92066311426942e-05 +/- 0.0001776198934280826</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.0001776198934280937 +/- 0.0003552397868561134</t>
+          <t>0.0002368265245707435 +/- 0.00041444641799881504</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.0001184132622853995 +/- 0.001533668898400062</t>
+          <t>0.0005328596802841812 +/- 0.0011295905286168703</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.011101243339253974 +/- 0.0026519350010611262</t>
+          <t>-0.03206039076376556 +/- 0.003987227044950613</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-0.0007696862048548914 +/- 0.00040155890959889387</t>
+          <t>5.9206631142671995e-05 +/- 0.0007582148297730045</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.001184132622853784 +/- 0.000577074857596728</t>
+          <t>-0.002161042036708127 +/- 0.0008482266892773349</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0008288928359976522 +/- 0.0008456398376012756</t>
+          <t>0.008111308466548228 +/- 0.0014209591474245028</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.002693901716992286 +/- 0.001223802641124606</t>
+          <t>-0.006779159265837775 +/- 0.002217088732190955</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.000828892835997641 +/- 0.00047365304914150915</t>
+          <t>0.0018354055654233425 +/- 0.0009435984280940812</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.0005032563647128785 +/- 0.0010173380862900892</t>
+          <t>-2.9603315571369303e-05 +/- 0.0014038964714481058</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.006127886323268184 +/- 0.001695678329380671</t>
+          <t>-0.015156897572528139 +/- 0.0015141162643628587</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.005358200118413292 +/- 0.0015062823248322569</t>
+          <t>0.004558910597986976 +/- 0.0018065300535692666</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0012729425695678254 +/- 0.001900385298484788</t>
+          <t>0.006542332741266999 +/- 0.0010792022577595156</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.0024570751924215426 +/- 0.0007948917455356726</t>
+          <t>-0.0009473060982830072 +/- 0.001348820100638809</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.00159857904085261 +/- 0.0009191340850361238</t>
+          <t>-0.002841918294849033 +/- 0.001522197765800159</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.0017465956187093234 +/- 0.0011423197976065487</t>
+          <t>0.007223208999407915 +/- 0.0008182519219115187</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-2.9603315571302692e-05 +/- 0.0004279701685849688</t>
+          <t>-0.0002072232089994186 +/- 0.0005928059323416563</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.003137951450562437 +/- 0.0016546108481328792</t>
+          <t>0.004410894020130252 +/- 0.0018883574225952548</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.008762581409117865 +/- 0.0017423255144537737</t>
+          <t>0.010242747187684998 +/- 0.002030364499642653</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0004440497335701954 +/- 0.0017774319777712536</t>
+          <t>0.001598579040852577 +/- 0.0011013070004581534</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.004085257548845489 +/- 0.0016365038438229762</t>
+          <t>0.0015985790408525658 +/- 0.0017271701771243162</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.001154529307282448 +/- 0.0007882490796740333</t>
+          <t>-0.000799289520426294 +/- 0.00029750963946478435</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.0004736530491415314 +/- 0.0003018957675306575</t>
+          <t>0.002427471876850196 +/- 0.00047365304914148275</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.0002072232089993631 +/- 0.00018955370744321734</t>
+          <t>-0.0015689757252812186 +/- 0.0004196994339478293</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.0009473060982829629 +/- 0.001770268370364247</t>
+          <t>0.0019242155121373394 +/- 0.002251604129047539</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.0023386619301361987 +/- 0.001687388987566582</t>
+          <t>0.014091178211959755 +/- 0.0013707326113428242</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,147 +2951,147 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>0.0005624629958555505 +/- 0.0006546283122408534</t>
+          <t>0.0007992895204262717 +/- 0.00047825619956789285</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.002782711663706372 +/- 0.0013834602066960246</t>
+          <t>0.003759621077560682 +/- 0.000898400882504042</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.0016577856719952489 +/- 0.0017322366889671792</t>
+          <t>0.002249851983422135 +/- 0.0018306246102712067</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.0013025458851391725 +/- 0.00044306185752209843</t>
+          <t>-0.001628182356423924 +/- 0.0009384764644255171</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.004026050917702795 +/- 0.0012503677964442231</t>
+          <t>0.000858496151568977 +/- 0.0015966591545484804</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.003552397868561319 +/- 0.001560855692890945</t>
+          <t>-0.002989934872705757 +/- 0.0013465441581461202</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.0015393724097098494 +/- 0.0009153123051356063</t>
+          <t>-0.0037892243931320403 +/- 0.0016095058873970389</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.006157489638839553 +/- 0.0011526300967396018</t>
+          <t>0.0009473060982829962 +/- 0.0013998330867421005</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-8.880994671399689e-05 +/- 0.0003982718782437391</t>
+          <t>-0.0003552397868561541 +/- 0.00029005207137753264</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.0030491415038484625 +/- 0.0015834315121748214</t>
+          <t>-0.003996447602131447 +/- 0.000947768537216234</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.001953818827708731 +/- 0.0016912796752025637</t>
+          <t>-0.0031083481349911237 +/- 0.001351740681685107</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.0005920663114268532 +/- 0.0006349203845330831</t>
+          <t>-0.001568975725281252 +/- 0.0008885927187568617</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.008496151568975763 +/- 0.00163784205963565</t>
+          <t>0.010005920663114265 +/- 0.001984967982740101</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.0014801657785671774 +/- 0.0007371166132616288</t>
+          <t>-0.0029899348727057463 +/- 0.001340020165512876</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.001953818827708753 +/- 0.0016860900966131672</t>
+          <t>0.0014209591474245054 +/- 0.0011060711481509602</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.0001480165778567466 +/- 0.00040264862370441323</t>
+          <t>0.0002664298401420795 +/- 0.0002792771205463542</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.0004440497335701954 +/- 0.0008294212981717978</t>
+          <t>-0.0023090586145648297 +/- 0.001219139152277919</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.000296033155713471 +/- 0.0007605229472270628</t>
+          <t>-0.004973357015985791 +/- 0.0013092566244817226</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>0.0002072232089994297 +/- 0.00013565943442736298</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.0005328596802841479 +/- 0.0007809891035093443</t>
+          <t>0.0005328596802841923 +/- 0.0006853663056714213</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.008762581409117842 +/- 0.0012291616040276203</t>
+          <t>-0.003966844286560111 +/- 0.002346704698946885</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-2.9603315571335997e-05 +/- 8.880994671400799e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0002664298401421128 +/- 0.0005369555105747915</t>
+          <t>0.00014801657785670219 +/- 0.00035647112429816933</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.003670811130846685 +/- 0.0012433392539964426</t>
+          <t>0.0005920663114268754 +/- 0.0017261550902443262</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.007193605683836623 +/- 0.001199208354086984</t>
+          <t>-0.0029899348727057463 +/- 0.0015464722186629956</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0013617525162818445 +/- 0.000532859680284196</t>
+          <t>-0.0007400828892835998 +/- 0.0006519453980327243</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.0010953226761397205 +/- 0.0013109289417101598</t>
+          <t>-0.004766133806986395 +/- 0.0011874583256442572</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.004114860864416836 +/- 0.001580107299595329</t>
+          <t>0.008614564831261074 +/- 0.0016717356901711855</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.004322084073416199 +/- 0.0010933206224167846</t>
+          <t>-0.0018058022498519954 +/- 0.00120939598672677</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.003165151989971815 +/- 0.0018243534412820772</t>
+          <t>0.0037292384832341096 +/- 0.0009551708338532114</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.000564086493262328 +/- 0.001657073527596644</t>
+          <t>0.004073958006894407 +/- 0.0018002389992284764</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.009307427138827918 +/- 0.0011645818975908485</t>
+          <t>0.010686305233469163 +/- 0.0012492091148852823</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.0008774678784080226 +/- 0.0007118656654089995</t>
+          <t>0.0028831087433406565 +/- 0.001119434102130474</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0010028204324663004 +/- 0.002188290849275608</t>
+          <t>0.0022876841115638037 +/- 0.0013519056477670347</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.0026010654967095204 +/- 0.0015032510128751308</t>
+          <t>0.002789094327796948 +/- 0.0011163593312790384</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.00012535255405826673 +/- 0.00031958755961095266</t>
+          <t>6.267627702915002e-05 +/- 0.0002731995577273991</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.003760576621748668 +/- 0.0012613357441239761</t>
+          <t>-0.0011908492635537393 +/- 0.0009380526196863584</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.00012535255405827784 +/- 0.002221252917163189</t>
+          <t>0.005578188655593874 +/- 0.0029257135736719076</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.015010968348480092 +/- 0.0028805528708988944</t>
+          <t>0.02127859605139456 +/- 0.0037877686074368785</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.003259166405515512 +/- 0.0017290020964128795</t>
+          <t>-0.004136634283923535 +/- 0.0013132138414137875</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.007458476966468186 +/- 0.0017549357568160556</t>
+          <t>0.0072077718583516415 +/- 0.0011641601768102026</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.0026324036352240675 +/- 0.0017515748809128276</t>
+          <t>0.0014728925101849088 +/- 0.0020214921244588054</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.004763397054214991 +/- 0.0014209694827646017</t>
+          <t>-0.004042619868379805 +/- 0.00253219140369988</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.0026324036352240567 +/- 0.0013236422489466034</t>
+          <t>0.01300532748354749 +/- 0.00199311546426298</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.0040426198683798376 +/- 0.0008690331948519076</t>
+          <t>-0.004544030084612949 +/- 0.0011662672557773938</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.0009401441554371503 +/- 0.0010008598823360358</t>
+          <t>0.0033845189595738236 +/- 0.0009587626788328659</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0013475399561265866 +/- 0.0019269770153109663</t>
+          <t>0.004512691946098402 +/- 0.0008885895881389951</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.0005014102162331669 +/- 0.0010506458548567908</t>
+          <t>-6.267627702912781e-05 +/- 0.0008616563512922265</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.000532748354747714 +/- 0.0003149443942689243</t>
+          <t>6.267627702913892e-05 +/- 0.00018802883108741676</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.00604826073331245 +/- 0.0011561182541959566</t>
+          <t>0.0017862738953306257 +/- 0.0014635279760370561</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.002130993418990901 +/- 0.0011708894824361965</t>
+          <t>0.004011281729865257 +/- 0.0016089624134118868</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.001629583202757723 +/- 0.0006391751192219184</t>
+          <t>0.0016295832027577672 +/- 0.0009890149694803938</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0035412096521466375 +/- 0.0009815393145324854</t>
+          <t>0.0013162018176120615 +/- 0.000520628258409152</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.0031651519899717926 +/- 0.00120926238681132</t>
+          <t>0.0008774678784080336 +/- 0.001187545930523133</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.00015669069257283618 +/- 0.0005649563264594177</t>
+          <t>-0.00025070510811656674 +/- 0.0005014102162331614</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.003885929175806946 +/- 0.0011825736298410074</t>
+          <t>0.008492635537449089 +/- 0.0014861680603421364</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.002444374804136629 +/- 0.0009790347447078242</t>
+          <t>0.004638044500156702 +/- 0.0011194341021304724</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.003384518959573801 +/- 0.0008267568761061017</t>
+          <t>0.00501410216233158 +/- 0.0013072173998504794</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.005797555625195861 +/- 0.0006306678720619785</t>
+          <t>0.0049514258853024405 +/- 0.001145450760419738</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.00018802883108743896 +/- 0.000319587559610957</t>
+          <t>0.0006894390473205947 +/- 0.0004157473883240898</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.00047007207771857515 +/- 0.00040254567780210695</t>
+          <t>0.0009714822939517643 +/- 0.0005139836874602497</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.0009401441554371725 +/- 0.0007282325314084747</t>
+          <t>0.0013788780946412005 +/- 0.0010873927654589314</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.0017549357568160673 +/- 0.0014645341830834143</t>
+          <t>-0.003917267314321504 +/- 0.0013090942384334193</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>3.133813851456946e-05 +/- 0.0006490854019808272</t>
+          <t>6.267627702917222e-05 +/- 0.0005391617215319664</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.0003447195236603084 +/- 0.0006490854019808143</t>
+          <t>0.0003447195236603084 +/- 0.0004945074847401939</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.00012535255405827784 +/- 0.0009929789732218718</t>
+          <t>0.0020369790034472147 +/- 0.0010226993965578653</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>0.0023816985271074677 +/- 0.0010691771926814176</t>
+          <t>0.007646505797555636 +/- 0.0016235454524586089</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.0008147916013788725 +/- 0.0009211493861923608</t>
+          <t>0.0015669069257286284 +/- 0.0005778467224877994</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.002130993418990923 +/- 0.0007118656654090151</t>
+          <t>-0.0008774678784080114 +/- 0.0009790347447078218</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.0017862738953306368 +/- 0.001253917206126128</t>
+          <t>9.401441554374168e-05 +/- 0.001206009489495094</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0002193669696019973 +/- 0.001011110360695823</t>
+          <t>0.0051081165778752765 +/- 0.0009510492576304366</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.00109683484801002 +/- 0.0013962187032244035</t>
+          <t>0.004606706361642144 +/- 0.0014768877051643092</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.004544030084612993 +/- 0.0016715305989463637</t>
+          <t>0.002601065496709509 +/- 0.0013877524177677582</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.00028204324663116953 +/- 0.0019188053293439998</t>
+          <t>0.0006581009088060475 +/- 0.001043611770939923</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.0008774678784080447 +/- 0.0011792471151505328</t>
+          <t>0.0009401441554371948 +/- 0.001957066122970356</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.0004700720777186085 +/- 0.0007834534628643076</t>
+          <t>-0.0006894390473205836 +/- 0.0006236210824861247</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0.0010028204324662893 +/- 0.0017881971316436405</t>
+          <t>0.002130993418990923 +/- 0.0009890149694803708</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.00021936696960201952 +/- 0.0013591506388092485</t>
+          <t>0.00479473519272956 +/- 0.0010950426330088492</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.006612347226574733 +/- 0.001954304209046547</t>
+          <t>0.001222187402068331 +/- 0.0014323277821405897</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.006330303979943608 +/- 0.0017153158487501182</t>
+          <t>0.0022876841115637815 +/- 0.001579703310702431</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.000595424631776853 +/- 0.0005508742034236122</t>
+          <t>-0.0003760576621748557 +/- 0.0007389424081825006</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.0007521153243497225 +/- 0.0007701789863644132</t>
+          <t>0.0008147916013788947 +/- 0.0006298887885377967</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>3.1338138514558354e-05 +/- 0.0003271797715108222</t>
+          <t>-0.0007521153243497336 +/- 0.0004250911929254402</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.0006894390473206169 +/- 0.0014140412626359746</t>
+          <t>-0.004293324976496404 +/- 0.001529159874491493</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.00235036038859292 +/- 0.0009322767020146448</t>
+          <t>0.0032591664055155343 +/- 0.0010412565168183116</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.0007834534628643364 +/- 0.0007958900093513206</t>
+          <t>9.401441554374168e-05 +/- 0.0005253229274283928</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0.004261986837981813 +/- 0.001717604463308656</t>
+          <t>-0.0002507051081165557 +/- 0.0014347255584154948</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.0022876841115638037 +/- 0.0019422062591471089</t>
+          <t>0.0036352240676904013 +/- 0.0013457167379243985</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.0001566906925728473 +/- 0.0006757711893716248</t>
+          <t>0.0005014102162331557 +/- 0.00034896674163774745</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.000658100908806003 +/- 0.0015883830645533282</t>
+          <t>0.0023503603885929427 +/- 0.0012554826464437573</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.0019429645879035062 +/- 0.0016391973463644024</t>
+          <t>0.002977123158884365 +/- 0.0009934733615886882</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0006581009088060363 +/- 0.001225397354811488</t>
+          <t>-0.0014102162331557366 +/- 0.0011320834765395278</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.00498276402381701 +/- 0.001303078839629706</t>
+          <t>0.002381698527107512 +/- 0.0007828264491881449</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>6.267627702913892e-05 +/- 0.00027319955772737623</t>
+          <t>9.401441554371948e-05 +/- 0.0002820432466311461</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.004011281729865268 +/- 0.0010927982309095997</t>
+          <t>0.004920087746787849 +/- 0.000919548777882873</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.0030711375744280735 +/- 0.0012281991815898115</t>
+          <t>0.002381698527107512 +/- 0.0008195986731821982</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0010341585709808588 +/- 0.0013519056477670102</t>
+          <t>0.0005327483547477252 +/- 0.0007289065089071175</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.004261986837981813 +/- 0.0019226401316424814</t>
+          <t>0.0007834534628643252 +/- 0.001706418475720714</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.00219366969602004 +/- 0.001094594120750436</t>
+          <t>0.005390159824506436 +/- 0.0009061004258728169</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.003415857098088393 +/- 0.001071471074727612</t>
+          <t>0.0039799435913506764 +/- 0.0010303530067548464</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>-0.00018802883108745005 +/- 0.0004250911929254287</t>
+          <t>9.401441554371948e-05 +/- 0.0003149443942689111</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-0.00153556878721407 +/- 0.0005508742034235945</t>
+          <t>-0.0009714822939517309 +/- 0.0010896483015176127</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.0009714822939517643 +/- 0.000822588827853781</t>
+          <t>-0.0003133813851457057 +/- 0.0005427924812187049</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,52 +3491,52 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.0006894390473206058 +/- 0.0007650614613433832</t>
+          <t>0.0020996552804763645 +/- 0.00048649873695582593</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.0017862738953306034 +/- 0.0010860371953095237</t>
+          <t>0.002601065496709509 +/- 0.0008757874404564157</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>0.0002507051081165557 +/- 0.00012535255405827782</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-0.0017862738953306144 +/- 0.0011128349047047751</t>
+          <t>-0.0005014102162331224 +/- 0.0003760576621748557</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.004324663115010963 +/- 0.0015656528983762927</t>
+          <t>0.00805390159824505 +/- 0.0008979347403255557</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.0007521153243497559 +/- 0.0011229378168078345</t>
+          <t>-0.0028831087433406344 +/- 0.0011106264585815768</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0025383892196803592 +/- 0.0006019859828360541</t>
+          <t>6.267627702915002e-05 +/- 0.001170889482436198</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.0022876841115637703 +/- 0.0016104876411820253</t>
+          <t>-0.0011908492635537393 +/- 0.0008501823858508616</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.007897210905672225 +/- 0.001686446135640694</t>
+          <t>0.0008774678784080336 +/- 0.001533969069322539</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>0.003791914760263215 +/- 0.0010986241393267332</t>
+          <t>0.0020056408649326563 +/- 0.0007309247126098863</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0021840873634945356 +/- 0.0013310907337099242</t>
+          <t>0.0016224648985959321 +/- 0.000944321120151115</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.004586583463338523 +/- 0.0026181175283367442</t>
+          <t>-0.0076443057722309195 +/- 0.001517356182937656</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.001996879875195001 +/- 0.0008956443116634692</t>
+          <t>0.00533541341653665 +/- 0.0011288644315210969</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.00046801872074880846 +/- 0.0007800312012480616</t>
+          <t>-0.002808112324493006 +/- 0.0012558260092042283</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0019968798751949677 +/- 0.001964440092193096</t>
+          <t>0.005709828393135696 +/- 0.0013387480781856362</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.00804992199687985 +/- 0.0019475178201968472</t>
+          <t>0.003931357254290146 +/- 0.001646290915229096</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.00012480499219972297 +/- 0.0006271373242509098</t>
+          <t>-0.00021840873634948466 +/- 0.00028081123244929864</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.003400936037441482 +/- 0.0017784711388455668</t>
+          <t>0.005023400936037414 +/- 0.0021905409445826117</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.02074882995319811 +/- 0.004059161257802718</t>
+          <t>0.016380655226209018 +/- 0.0028020388471921556</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.016349453978159123 +/- 0.004195842864028526</t>
+          <t>0.023400936037441478 +/- 0.004193057704170303</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.000280811232449274 +/- 0.0014328814356574138</t>
+          <t>-0.0019344773790951897 +/- 0.0016439238530195814</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.003057722308892319 +/- 0.0015462729102482223</t>
+          <t>0.000624024960998415 +/- 0.0012480499219968883</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.0004992199687987809 +/- 0.0021760493945912895</t>
+          <t>0.0006864274570982709 +/- 0.0015462729102482242</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.014570982839313563 +/- 0.0020223126893103103</t>
+          <t>0.024898595943837733 +/- 0.0017021131603102509</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.01219968798751948 +/- 0.0029317553379155977</t>
+          <t>0.003962558502340063 +/- 0.0019834277785101676</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.00468018720748834 +/- 0.0008487657103735058</t>
+          <t>0.0017784711388455277 +/- 0.0012562135500278973</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.00012480499219970077 +/- 0.0013827469457822188</t>
+          <t>-0.0030265210608424577 +/- 0.0011926062311149149</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0013728549141965418 +/- 0.0011004800055256355</t>
+          <t>-0.002901716068642768 +/- 0.0009261043419441969</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.000624024960998415 +/- 0.0013600308716195401</t>
+          <t>-0.0010920436817473012 +/- 0.0010465216743368669</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.0009048361934477778 +/- 0.0004510712104462158</t>
+          <t>0.0008112324492979605 +/- 0.00028596416193172794</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.003962558502340063 +/- 0.0013460002876831917</t>
+          <t>0.003962558502340086 +/- 0.0006842967924949086</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.0021840873634945577 +/- 0.0014092467757424137</t>
+          <t>-0.0001872074882995456 +/- 0.001177407941598345</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.0016848673946958104 +/- 0.0009886414675665874</t>
+          <t>0.0004992199687987253 +/- 0.0007794069264771621</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.00028081123244930726 +/- 0.001187698365720688</t>
+          <t>0.00377535101404054 +/- 0.001297386763575142</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.0013104524180967414 +/- 0.0018814119727527327</t>
+          <t>0.003806552262090457 +/- 0.000823145457614539</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0007176287051482322 +/- 0.00037049429288730395</t>
+          <t>-0.00040561622464900803 +/- 0.00037049429288729923</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.002277691107644297 +/- 0.0021528861154446175</t>
+          <t>0.0014352574102963866 +/- 0.001974326617105317</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.0011544461778470905 +/- 0.0018775271617260901</t>
+          <t>0.004461778471138833 +/- 0.0013241245038329431</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.002433697347893926 +/- 0.0018448356317122539</t>
+          <t>-0.004960998439937625 +/- 0.001419228132985245</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.007082683307332316 +/- 0.0016215646128157591</t>
+          <t>-0.010078003120124811 +/- 0.0015728028906244528</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0004680187207488751 +/- 0.00044673388652969904</t>
+          <t>-0.00037441497659910226 +/- 0.00047932266757372787</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.0006240249609984428</t>
+          <t>-0.0008736349453978387 +/- 0.0006662763339801022</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.009360374414976636 +/- 0.0010626762162824666</t>
+          <t>-0.00574102964118568 +/- 0.0016639365523835783</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.0037753510140405844 +/- 0.0014664586583463435</t>
+          <t>-0.0017784711388456054 +/- 0.0010352985973814022</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-6.240249609986703e-05 +/- 0.00027200617432390957</t>
+          <t>0.00018720748829950117 +/- 0.0004669775209702166</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0004368174726988916 +/- 0.000938115218619215</t>
+          <t>3.120124804988356e-05 +/- 0.0006153848025995599</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.003057722308892341 +/- 0.001214846947515229</t>
+          <t>0.0021216848673946574 +/- 0.0014554638115058637</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.005585023400936062 +/- 0.0012359003008011343</t>
+          <t>-0.0012792511700468246 +/- 0.0013416536661466367</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.120124804995017e-05 +/- 0.000842433697347902</t>
+          <t>0.000967238689547556 +/- 0.0008424336973478739</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.0024960998439937376 +/- 0.0022714851448613206</t>
+          <t>0.001622464898595921 +/- 0.0016557253243583907</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.005054602184087387 +/- 0.0014147624397821735</t>
+          <t>-0.0023712948517941035 +/- 0.0020564439380073773</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.00071762870514821 +/- 0.0020029645985277854</t>
+          <t>0.0038377535101403737 +/- 0.0012168486739469677</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.009235569422776934 +/- 0.0008160185229717116</t>
+          <t>0.013042121684867358 +/- 0.0016790794442525633</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.0008424336973478885 +/- 0.0015789804591426029</t>
+          <t>0.0003120124804992019 +/- 0.0021115662172466413</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0003120124804992019 +/- 0.0010158390387581821</t>
+          <t>-0.0037441497659906676 +/- 0.0011506451740771158</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0031201248049921746 +/- 0.0017315989922635604</t>
+          <t>-0.003182527301092053 +/- 0.0012307696051991205</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.0004992199687987253 +/- 0.0004456429596594568</t>
+          <t>0.0006552262090483429 +/- 0.0005304212168486925</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0008424336973478774 +/- 0.000837798538664446</t>
+          <t>0.0008112324492979605 +/- 0.00082786266217919</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.010140405616224623 +/- 0.0013474460456592231</t>
+          <t>0.005429017160686412 +/- 0.001646290915229058</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.010920436817472711 +/- 0.0009566121508115984</t>
+          <t>0.0006864274570982376 +/- 0.0014554638115058405</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.003556942277691133 +/- 0.001586054917583631</t>
+          <t>-0.0026521060842433996 +/- 0.002117321382505276</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.00015600624024962871 +/- 0.0007416451996258878</t>
+          <t>-0.00012480499219972297 +/- 0.0004456429596594724</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>-0.00015600624024962871 +/- 0.0002876612935192797</t>
+          <t>-0.001123244929797229 +/- 0.000740988585774592</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>3.120124804989466e-05 +/- 0.00021840873634945294</t>
+          <t>0.00021840873634941803 +/- 0.00014298208096583733</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.013010920436817498 +/- 0.0010812931950803964</t>
+          <t>-0.005709828393135763 +/- 0.0013093376136260428</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.0008736349453978387 +/- 0.0011987128057596474</t>
+          <t>0.0054290171606864 +/- 0.001310452418096727</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,147 +3841,147 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.0016536661466458602 +/- 0.0007390152438269486</t>
+          <t>-0.00012480499219972297 +/- 0.0005258127783573514</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.0006864274570983153 +/- 0.0011318787611367732</t>
+          <t>-0.0015912636505460598 +/- 0.0014123519872394766</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.005865834633385358 +/- 0.0014819771715491928</t>
+          <t>0.00162246489859591 +/- 0.0016557253243584078</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-9.36037441498061e-05 +/- 0.0008021815995121645</t>
+          <t>-0.0004992199687987919 +/- 0.00044564295965945997</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.00212168486739468 +/- 0.001314902184443386</t>
+          <t>0.0008112324492979495 +/- 0.0015361664430691053</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.005865834633385358 +/- 0.0012849460394367429</t>
+          <t>0.0015288611544461484 +/- 0.0011202073679261162</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0.0007800312012480104 +/- 0.002373141575014841</t>
+          <t>-0.003712948517940751 +/- 0.0016299479421664968</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.004305772230889226 +/- 0.0007617195392033559</t>
+          <t>0.000967238689547556 +/- 0.001066790701858294</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0.0002496099843993682 +/- 0.00027200617432391206</t>
+          <t>-3.1201248049927964e-05 +/- 9.360374414978389e-05</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.009297971918876735 +/- 0.0011987128057596537</t>
+          <t>0.0019344773790951563 +/- 0.0010790400290664858</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.003463338533541349 +/- 0.0018002336020906864</t>
+          <t>-0.0003432137285491632 +/- 0.0013048688715336402</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0002808112324492851 +/- 0.001048380506484337</t>
+          <t>-0.0010920436817473123 +/- 0.0005795374608738565</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.00829953198127924 +/- 0.001646290915229059</t>
+          <t>0.016474258970358802 +/- 0.001481977171549202</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.005865834633385391 +/- 0.0011573938839932168</t>
+          <t>0.0033073322932916983 +/- 0.0008736349453978364</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.0009984399375974728 +/- 0.001182358522402273</t>
+          <t>0.0021528861154445967 +/- 0.000818995616125206</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-0.00031201248049925743 +/- 0.0002790724464898495</t>
+          <t>0.0005304212168486422 +/- 0.0004638398985123024</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.00018720748829952337 +/- 0.000727731905752941</t>
+          <t>0.0003432137285491188 +/- 0.0005993564028798278</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.001123244929797207 +/- 0.0008395397221262628</t>
+          <t>6.240249609983373e-05 +/- 0.0006363830906200193</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
+          <t>3.1201248049916865e-05 +/- 9.360374414975059e-05</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>0.0006864274570982709 +/- 0.0003897034632385984</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>0.0009672386895475671 +/- 0.0008874547677583797</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>0.000624024960998415 +/- 0.0005404214688202498</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>0.002683307332293272 +/- 0.0008624196543578856</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.0009672386895476004 +/- 0.0005993564028798145</t>
+          <t>-0.0004368174726989582 +/- 0.0005616224648985936</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.0033697347893916095 +/- 0.0013000103997503696</t>
+          <t>-0.0004992199687987809 +/- 0.0010826428438625482</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.00015600624024960651 +/- 0.0015985882630202327</t>
+          <t>0.005054602184087331 +/- 0.0011573938839932205</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.0004056162246489969 +/- 0.0011254095973086597</t>
+          <t>-2.2204460492503132e-17 +/- 0.00048336765631293744</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0009984399375975062 +/- 0.0011232449297971859</t>
+          <t>3.120124804990576e-05 +/- 0.0010201424476924813</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.006864274570982809 +/- 0.0009566121508115911</t>
+          <t>0.004680187207488284 +/- 0.00108084293764049</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.003837753510140385 +/- 0.0008377985386644262</t>
+          <t>-0.0016848673946958104 +/- 0.0008510565801551106</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0032714412024756447 +/- 0.0007273187550399677</t>
+          <t>-0.002092543471853836 +/- 0.0014284256782850068</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.006307102858826963 +/- 0.0018462080475527018</t>
+          <t>0.013262599469496017 +/- 0.0019416055516652678</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.003654582964927744 +/- 0.001158083271699881</t>
+          <t>0.008193339227821972 +/- 0.0019000013511684254</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.002063071028588237 +/- 0.0016776008807259202</t>
+          <t>0.0014736221632773328 +/- 0.0012914177601064754</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0025935750073680765 +/- 0.00162392894947902</t>
+          <t>0.0075744179192454904 +/- 0.0023542930071961637</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.003978779840848767 +/- 0.001827529148002064</t>
+          <t>0.0012967875036840493 +/- 0.0028275119257792835</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00014736221632770662 +/- 0.00023761443407893854</t>
+          <t>2.9472443265532446e-05 +/- 0.000596043277811854</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.007397583259652185 +/- 0.0008278556973290884</t>
+          <t>0.004892425582080728 +/- 0.00165780856002656</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.041585617447686386 +/- 0.0025607126861474623</t>
+          <t>0.03978779840848806 +/- 0.0027960014678765728</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.05520188623636897 +/- 0.0015709116382241514</t>
+          <t>0.0399351606248158 +/- 0.0020892199939224524</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.0015030946065429207 +/- 0.0015396354714540673</t>
+          <t>-0.005923961096374897 +/- 0.0019658362682761347</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.009873268493958132 +/- 0.0015441422808640981</t>
+          <t>0.006660772178013552 +/- 0.0008252284114352892</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.024255820807544903 +/- 0.002088388298032044</t>
+          <t>0.022575891541408766 +/- 0.0014085238013968138</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.002888299440023556 +/- 0.0021121689203853805</t>
+          <t>-0.00716180371352787 +/- 0.0032608032060049883</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.03135867963454168 +/- 0.0019018291547187479</t>
+          <t>0.02788093132920717 +/- 0.0019997872624447337</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.0008252284114352637 +/- 0.001777166334415719</t>
+          <t>0.006218685529030332 +/- 0.00173086317241687</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-8.841732979666394e-05 +/- 0.0006463811435149494</t>
+          <t>0.0019451812555260739 +/- 0.0010478272227899346</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.0036251105216622225 +/- 0.0015373771123778392</t>
+          <t>0.0026819923371647404 +/- 0.0021595479047123115</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.004037724727379876 +/- 0.0012367895819839377</t>
+          <t>0.003094606542882394 +/- 0.000952739750972272</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.0003831417624520772 +/- 0.0003499658734759062</t>
+          <t>0.00014736221632771773 +/- 0.00044208664898319754</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.010669024462127941 +/- 0.0017175127950879283</t>
+          <t>-0.01794871794871795 +/- 0.0023483823297213422</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0007957559681697202 +/- 0.0014561295994147659</t>
+          <t>0.0024756852343059133 +/- 0.0012022445065942408</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.00406719717064542 +/- 0.0010020630710286093</t>
+          <t>0.004479811376363075 +/- 0.0011847775562771313</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.007102858826996727 +/- 0.0012325684448173438</t>
+          <t>0.001797819039198345 +/- 0.000638267251037657</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.006159740642499245 +/- 0.0007736165486829724</t>
+          <t>0.00017683465959327237 +/- 0.0016525606565135592</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0005305039787798172 +/- 0.0005560849473655378</t>
+          <t>-0.00047155909224876335 +/- 0.0007362213968050188</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.007544945475979936 +/- 0.001202244506594215</t>
+          <t>0.006159740642499256 +/- 0.0015786338627576766</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.007633362805776633 +/- 0.0015896005375964394</t>
+          <t>-0.010403772472738004 +/- 0.0010128405704355834</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-0.004833480695549686 +/- 0.0011429837565379093</t>
+          <t>-0.0013852048334807021 +/- 0.0009779345725338734</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.00551134689065721 +/- 0.0013509185542429649</t>
+          <t>-0.004509283819628662 +/- 0.0013249494130851075</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0006189213085764589 +/- 0.00038314176245211396</t>
+          <t>0.001178897730621864 +/- 0.000995104215510403</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.0005010315355142847 +/- 0.00041784399878449596</t>
+          <t>0.0027114647804302614 +/- 0.0005714918782689491</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.0014146772767462679 +/- 0.0008521563392160948</t>
+          <t>0.0014736221632773217 +/- 0.0008336065796481479</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.003153551429413537 +/- 0.0012507571573193545</t>
+          <t>-0.007987032124963166 +/- 0.001852079851855597</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-5.894488653115371e-05 +/- 0.00039099614386742764</t>
+          <t>0.0010020630710285694 +/- 0.00037743143161999177</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.0007662835249042432 +/- 0.0007122337738635189</t>
+          <t>-0.00029472443265546875 +/- 0.0006590238660476572</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.0005305039787798727 +/- 0.0012559549515274097</t>
+          <t>0.007633362805776578 +/- 0.001189533514330124</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0019451812555260628 +/- 0.0018834713007569118</t>
+          <t>-0.007220748600058957 +/- 0.001358612504758739</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0009136457412319277 +/- 0.0007847643357320407</t>
+          <t>0.004980842911877392 +/- 0.0009725906277630406</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.007721780135573198 +/- 0.0009207485618516538</t>
+          <t>0.0043619216033009 +/- 0.0012065717353644998</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.004067197170645487 +/- 0.0015359639517589715</t>
+          <t>-0.006601827291482465 +/- 0.0014570241195765716</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0018272914824638664 +/- 0.0018816256645460855</t>
+          <t>0.006631299734747975 +/- 0.002891455477504949</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.0024167403477748594 +/- 0.0009016833799456994</t>
+          <t>0.007780725022104329 +/- 0.001237842617152977</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.00200412614205715 +/- 0.0025312007726005117</t>
+          <t>0.001444149720011778 +/- 0.0014879935822415906</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.0029767167698202535 +/- 0.0011524441376962863</t>
+          <t>-0.003271441202475689 +/- 0.0010581387015040644</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.001061007957559723 +/- 0.001172988431602287</t>
+          <t>-0.001473622163277366 +/- 0.0016981857106852802</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.0005305039787798727 +/- 0.00039099614386741766</t>
+          <t>-0.00020630710285886035 +/- 0.000672721026260726</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.002387267904509238 +/- 0.0009725906277630518</t>
+          <t>0.008429118773946342 +/- 0.0011949976382383482</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.00123784261715294 +/- 0.0015969604696898444</t>
+          <t>0.004214559386973149 +/- 0.0009690116252740236</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.008753315649867343 +/- 0.0014014139025014494</t>
+          <t>0.009608016504568228 +/- 0.0011877065534695082</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.004214559386973138 +/- 0.0021049597802144473</t>
+          <t>-0.006926024167403488 +/- 0.002226096386770595</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>0.0003831417624520883 +/- 0.0008944291721481558</t>
+          <t>0.0019157088122605192 +/- 0.000514714093621353</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.000884173297966373 +/- 0.00041680328982407987</t>
+          <t>0.0006483937518420135 +/- 0.0006011222532971001</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>-0.0011199528440907658 +/- 0.00011788977306217417</t>
+          <t>-0.000854700854700885 +/- 0.00042607816960805355</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.0011494252873563537 +/- 0.0017458536067927865</t>
+          <t>0.0004420866489831865 +/- 0.002402501309159188</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.0024462127910404143 +/- 0.002096690411061865</t>
+          <t>0.0006483937518419914 +/- 0.0022515094906907546</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0010020630710286028 +/- 0.000441103140203244</t>
+          <t>-0.0005010315355143069 +/- 0.0008022786671863474</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.0035661656351311357 +/- 0.000907923477792486</t>
+          <t>-0.001679929266136182 +/- 0.0015486359747031728</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>0.002534630120836967 +/- 0.0019997872624447125</t>
+          <t>-0.00026525198938994745 +/- 0.0014703766204852762</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.000884173297966373 +/- 0.0008439623379473302</t>
+          <t>-0.0016504568228706495 +/- 0.0006210229149927771</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.005039787798408524 +/- 0.0016004920698361915</t>
+          <t>0.00604185086943706 +/- 0.0016209843796050575</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.004008252284114366 +/- 0.0019335360408908725</t>
+          <t>0.005982905982905984 +/- 0.002426962201714147</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.00026525198938989194 +/- 0.0018660968014473037</t>
+          <t>0.004656646035956347 +/- 0.0022047278761290925</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-0.006483937518420313 +/- 0.0012223071826305543</t>
+          <t>-0.0034482758620689945 +/- 0.0017288546272988458</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-8.841732979666394e-05 +/- 0.00023018714046293284</t>
+          <t>8.841732979663064e-05 +/- 0.00018871571580996642</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.007279693486590089 +/- 0.001229746303862375</t>
+          <t>-0.0032419687592101566 +/- 0.0009504577363157816</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.0014441497200118002 +/- 0.0009990245362026756</t>
+          <t>-0.0005305039787798615 +/- 0.0012208850679167672</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.001061007957559712 +/- 0.0008356879975689896</t>
+          <t>0.00215148835838489 +/- 0.001311772065090935</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.003654582964927744 +/- 0.002245328258737505</t>
+          <t>0.007397583259652218 +/- 0.00225401577424095</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.001562039493074019 +/- 0.0011718771206643765</t>
+          <t>-0.008664898320070747 +/- 0.0014510502357902872</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-0.0005305039787798727 +/- 0.0015584207564282174</t>
+          <t>-0.0024756852343059466 +/- 0.0015438609907113276</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-8.841732979666394e-05 +/- 0.0003241968759210204</t>
+          <t>0.0003831417624520883 +/- 0.0002961943890692922</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.001827291482463933 +/- 0.0007195140357048808</t>
+          <t>-0.0017978190391983672 +/- 0.0006517342878719518</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.001002063071028625 +/- 0.0006616547103048448</t>
+          <t>-0.0007073386383731562 +/- 0.0011877065534694911</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,52 +4381,52 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.003772472737990018 +/- 0.00039099614386744607</t>
+          <t>-0.0018862363689949979 +/- 0.0012724452192704263</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.0040082522841143105 +/- 0.0006999317469518461</t>
+          <t>0.00123784261715294 +/- 0.0017124478687101556</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.0021220159151193905 +/- 0.00017683465959330568</t>
+          <t>-0.00026525198938989194 +/- 8.841732979663064e-05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-0.000707338638373145 +/- 0.000496678442273881</t>
+          <t>-0.0002652519893899141 +/- 0.0007391651166510152</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.0068376068376068576 +/- 0.0008622893509182311</t>
+          <t>0.003743000294724419 +/- 0.0010465830182472423</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>-0.006660772178013585 +/- 0.0007479267633627793</t>
+          <t>-0.011258473327438867 +/- 0.0017820473277725959</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.0031240789861479825 +/- 0.0009150707159599392</t>
+          <t>-0.004185086943707661 +/- 0.0007886288334959964</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.0006778661951075571 +/- 0.0010382502183205837</t>
+          <t>0.003124078986147927 +/- 0.0015827552705095908</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.0010904804008252445 +/- 0.001910259996828627</t>
+          <t>-0.011936339522546436 +/- 0.0014984643464646156</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>-0.0017094017094017588 +/- 0.0008210072665596301</t>
+          <t>0.002416740347774826 +/- 0.001460596721881982</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0012100259291270676 +/- 0.0009963478228631796</t>
+          <t>-0.00328435609334492 +/- 0.0008945073290844042</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.0002304811293575071 +/- 0.00151246381427907</t>
+          <t>-0.002881014116969227 +/- 0.0013012491835939061</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.015643906655142592 +/- 0.0014861677184130168</t>
+          <t>-0.004062229904926584 +/- 0.001465923852861818</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.004091040046096228 +/- 0.002278734650911594</t>
+          <t>0.005762028233938288 +/- 0.0016799054724417357</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.0012388360702967338 +/- 0.001690003961516855</t>
+          <t>-0.016162489196197116 +/- 0.0019173359990751742</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.001555747623163317 +/- 0.00168089336166118</t>
+          <t>0.0024776721405934455 +/- 0.0014474049769035264</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.00014405070584846413 +/- 0.0002656163773348623</t>
+          <t>-0.00037453183520603784 +/- 0.0003169115528666086</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0032843560933448535 +/- 0.001453128229665063</t>
+          <t>-0.001152405646787724 +/- 0.0012623971362838978</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.0007490636704119647 +/- 0.0028409779396418463</t>
+          <t>-0.002016709881878476 +/- 0.0038068652628427476</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0021895707288965838 +/- 0.002715499087974226</t>
+          <t>-0.005646787669259634 +/- 0.002913102773786113</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.011956208585422035 +/- 0.0012705892867300593</t>
+          <t>-0.0037165082108902904 +/- 0.0017780782626573841</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.011322385479688835 +/- 0.0018132087556968714</t>
+          <t>-0.017804667242869533 +/- 0.0019784828249368377</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.00605012964563526 +/- 0.0022939820498293906</t>
+          <t>-0.0022760011524057154 +/- 0.0021188678776372046</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.012330740420628039 +/- 0.0017843690656527966</t>
+          <t>-0.014145779314318685 +/- 0.002099190000800552</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.008297320656871244 +/- 0.002553560334907572</t>
+          <t>0.009853068280034506 +/- 0.002566529236683381</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.004436761740132545 +/- 0.0010947853644482954</t>
+          <t>0.00302506482281758 +/- 0.0011469910249146914</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.006655142610198772 +/- 0.0013662812678051654</t>
+          <t>-0.0035724575050418263 +/- 0.00096589193974303</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.0011524056467876465 +/- 0.0011008339484035207</t>
+          <t>-0.004868913857677959 +/- 0.0006626332469029033</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.0005473926822241459 +/- 0.0009151472298627727</t>
+          <t>0.001267646211466389 +/- 0.0012371599281811565</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00023048112935751818 +/- 0.00017286084701815252</t>
+          <t>0.0005473926822240794 +/- 0.0003007867043765295</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.002881014116969183 +/- 0.0015353399705530686</t>
+          <t>-0.006222990492653469 +/- 0.0012637114491190688</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.0011235955056180136 +/- 0.0014602507516536041</t>
+          <t>-0.0008354940939211075 +/- 0.002161528721625212</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0039469893402477975 +/- 0.0008051390730326842</t>
+          <t>0.002794583693460073 +/- 0.0011161838448752728</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.005963699222126195 +/- 0.0012361531519979832</t>
+          <t>0.003486027081532661 +/- 0.0015803616423972892</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.006799193316047269 +/- 0.0008851795733642941</t>
+          <t>0.0012388360702967004 +/- 0.001469317199654287</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.00014405070584847524 +/- 0.0006212578119518166</t>
+          <t>0.0018438490348602233 +/- 0.0003907997685465476</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0009507346585998389 +/- 0.0014465445359415922</t>
+          <t>0.005992509363295817 +/- 0.0017083223371217092</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.008873523480265077 +/- 0.0013189885499578782</t>
+          <t>0.009737827715355774 +/- 0.0016030455480545798</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.004235090751944693 +/- 0.0009472360831330319</t>
+          <t>-0.006078939786804993 +/- 0.0012321178208206684</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.004494382022471899 +/- 0.0023553942305928667</t>
+          <t>-0.01740132526649386 +/- 0.0022323676897505655</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.001094785364448314 +/- 0.0005435886564135242</t>
+          <t>-0.0002304811293575848 +/- 0.00042342087169976313</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.0004321521175454035 +/- 0.0005193822062034024</t>
+          <t>0.0008931143762603844 +/- 0.0005826490468498216</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.002131950446557207 +/- 0.001734360926913556</t>
+          <t>-0.0010947853644483363 +/- 0.0010210340044177106</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.005416306539902049 +/- 0.0011509642382851193</t>
+          <t>0.005214635551714142 +/- 0.0013355605861710331</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.0006914433880726101 +/- 0.0008169084920056468</t>
+          <t>-0.001210025929127112 +/- 0.000628563072004368</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.0006338231057332111 +/- 0.0004425897866821417</t>
+          <t>-0.00014405070584850855 +/- 0.0006601232634623515</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.0026505329876116645 +/- 0.0013439243779533954</t>
+          <t>0.0030250648228175915 +/- 0.0010721863477918992</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.0017574186113512135 +/- 0.0013963262248404145</t>
+          <t>0.004926534140017247 +/- 0.0011699187844567628</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.0003457216940362717 +/- 0.0007600637256279405</t>
+          <t>-0.0019878997407087986 +/- 0.0006992025986465914</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.003802938634399333 +/- 0.0009879820339661338</t>
+          <t>0.0033707865168538854 +/- 0.001215842572515654</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0012964563526361328 +/- 0.001056590078991206</t>
+          <t>0.0030538749639872687 +/- 0.0012897164670469363</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.0019590895995390102 +/- 0.0009000575829336293</t>
+          <t>-0.009420916162489246 +/- 0.001491742260558877</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.009968308844713303 +/- 0.0008066839527513636</t>
+          <t>-0.010112359550561844 +/- 0.0012848806177457532</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.0034860270815326943 +/- 0.0015751007701338773</t>
+          <t>0.007634687409968255 +/- 0.0017441441506961038</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.002996254681647925 +/- 0.0012168661528056848</t>
+          <t>-0.0016709881878421596 +/- 0.001129122324532752</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.005358686257562628 +/- 0.0011247030421171478</t>
+          <t>-0.0038029386343993777 +/- 0.0012806747779252647</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.000403341976375704 +/- 0.0005185825410544379</t>
+          <t>0.0017286084701814476 +/- 0.0006311985681419299</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.005214635551714197 +/- 0.0006239241667446735</t>
+          <t>-0.0008931143762604954 +/- 0.0010659752232785801</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.013771247479112647 +/- 0.0015342583642401937</t>
+          <t>-0.01339671564390671 +/- 0.0014984043358047749</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.0246902909824258 +/- 0.0015835097762790316</t>
+          <t>-0.02301930279458375 +/- 0.001211739605002185</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.011495246326706999 +/- 0.0007451752899094165</t>
+          <t>-0.02278882166522621 +/- 0.0009934278104043147</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.0004033419763756818 +/- 0.000564561162266344</t>
+          <t>0.0018726591760299116 +/- 0.0006848092379144243</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5.762028233937677e-05 +/- 0.0008025576650639103</t>
+          <t>0.0010947853644482364 +/- 0.0006544406045289899</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-0.0015269374819936398 +/- 0.0003655597101829301</t>
+          <t>-0.0008066839527514303 +/- 0.0006914433880726083</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.01596081820800922 +/- 0.0023659423990374795</t>
+          <t>-0.0277153558052435 +/- 0.001386483366812553</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.016969173148948413 +/- 0.0020267683476763495</t>
+          <t>-0.01961970613656012 +/- 0.001169918784456735</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,147 +4731,147 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-0.00046096225871504747 +/- 0.0008270066317722317</t>
+          <t>0.0002304811293574849 +/- 0.000495668410662187</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-0.004494382022471877 +/- 0.0015947395566808392</t>
+          <t>-0.009997118985883091 +/- 0.001195186892117045</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.01097666378565253 +/- 0.0012521644374589972</t>
+          <t>-0.012186689714779663 +/- 0.0012758046571872538</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.0004321521175453924 +/- 0.0006968243516247545</t>
+          <t>0.0009795447997694717 +/- 0.0006842029436495515</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.00014405070584845304 +/- 0.001154204876059354</t>
+          <t>-0.007634687409968377 +/- 0.001690985951118305</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.020023048112935725 +/- 0.0012771051719562933</t>
+          <t>-0.032757130509939544 +/- 0.0013079296413501728</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.0008354940939210743 +/- 0.001993736707207831</t>
+          <t>0.003341976375684197 +/- 0.0007858358799761165</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.01400172860847021 +/- 0.0017581269147095545</t>
+          <t>-0.000460962258715103 +/- 0.0010242805436261094</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.0010083549409392156 +/- 0.0003221071704839973</t>
+          <t>0.004465571881302155 +/- 0.0003469200397232111</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.010227600115240576 +/- 0.001365065714835188</t>
+          <t>0.011552866609046319 +/- 0.001148437420224421</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.0031691155286660997 +/- 0.0015244893754333582</t>
+          <t>0.008959953903774076 +/- 0.0011265465166244314</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.0015845577643330833 +/- 0.0009748731959486308</t>
+          <t>0.00348602708153265 +/- 0.0006872290660833498</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.01371362719677328 +/- 0.0010871773128270214</t>
+          <t>0.018150388936905727 +/- 0.0016946633442641995</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.0076923076923077205 +/- 0.0010149187527403285</t>
+          <t>-0.0002304811293575848 +/- 0.000945042896390487</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.012244309997119018 +/- 0.0012574562283373884</t>
+          <t>0.00907519446845284 +/- 0.0016053738652555406</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-0.0002304811293575071 +/- 0.00021559535504312919</t>
+          <t>0.0011812157879573016 +/- 0.0002393150061342161</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.002852203975799483 +/- 0.0008394585009699468</t>
+          <t>0.00590607893978673 +/- 0.0010165530835135256</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.0008448791874742333</t>
+          <t>-0.0017286084701815586 +/- 0.0011008339484035062</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-0.0004321521175453258 +/- 0.0001932643022903656</t>
+          <t>5.762028233937677e-05 +/- 0.00011524056467875355</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.003255545952175187 +/- 0.0009205730514935212</t>
+          <t>0.006972054163065356 +/- 0.0007815995370930714</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.004609622587150697 +/- 0.001463373678962876</t>
+          <t>0.0018726591760299116 +/- 0.001470446575070554</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00012884286819357706</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-0.0003169115528665944 +/- 0.0007671291821200899</t>
+          <t>0.003975799481417397 +/- 0.0007921479161548614</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0038317487755689995 +/- 0.0012561353705901179</t>
+          <t>0.0026505329876115756 +/- 0.0009963478228631744</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.004148660328435638 +/- 0.0011538452546528699</t>
+          <t>0.00867185249207716 +/- 0.0014257381770853973</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.0026793431287812975 +/- 0.0009559585147241151</t>
+          <t>0.0041486603284355385 +/- 0.0013525433125100039</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>0.0015557476231633615 +/- 0.0010717992070145982</t>
+          <t>0.004436761740132478 +/- 0.0016154244619851642</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.006626332469029106 +/- 0.001262397136283875</t>
+          <t>0.013511956208585363 +/- 0.0013662812678051687</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.00210314030538753 +/- 0.0005769226273264438</t>
+          <t>0.00279458369346004 +/- 0.0014579753303232208</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.003569303985722738 +/- 0.0009405941880334465</t>
+          <t>-0.00327186198691255 +/- 0.0017994626367940744</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.003123140987507389 +/- 0.0019696410625988452</t>
+          <t>-0.005889351576442592 +/- 0.0014620113893449743</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0022010707911957585 +/- 0.0007548231731379732</t>
+          <t>-0.00041641879833431705 +/- 0.0013315305940273224</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.005413444378346266 +/- 0.0009756823002294353</t>
+          <t>0.002022605591909599 +/- 0.001232142485259257</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.004045211183819131 +/- 0.000777911768627117</t>
+          <t>-0.0015764425936942272 +/- 0.0018767152354964335</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.003955978584176112 +/- 0.001296860758869246</t>
+          <t>0.005978584176085666 +/- 0.0017719656167289137</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.9744199881076573e-05 +/- 0.00031053856362020846</t>
+          <t>5.9488399762053223e-05 +/- 0.000662434784393822</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.0031231409875074113 +/- 0.001090845973878195</t>
+          <t>-0.0045508625817965555 +/- 0.0015909671767181893</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.017578822129684757 +/- 0.0022316080287808093</t>
+          <t>0.016210588935157665 +/- 0.0026942729046893752</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.018233194527067252 +/- 0.002673836480424634</t>
+          <t>0.020582986317668073 +/- 0.0025441290636934173</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.0007733491969066253 +/- 0.0008943067446979734</t>
+          <t>-0.0014574657941701207 +/- 0.0014598918729099115</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0026174895895300088 +/- 0.0011657298002537438</t>
+          <t>8.923259964306318e-05 +/- 0.0009220701963117137</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.005710886377156499 +/- 0.0017637081594733565</t>
+          <t>0.0017251635930993325 +/- 0.0014800541706870593</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.018173706127305213 +/- 0.0014598918729099568</t>
+          <t>0.020464009518143957 +/- 0.002201070791195712</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.024033313503866793 +/- 0.0020252283796013243</t>
+          <t>0.023884592504461642 +/- 0.0026705256365589054</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0025282569898870235 +/- 0.0012353694025755754</t>
+          <t>-0.001814396192742407 +/- 0.0018644180778363928</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.004550862581796533 +/- 0.0013238675243466903</t>
+          <t>-0.0020523497917905977 +/- 0.001970539211784861</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-0.0007138607971445277 +/- 0.0012060163553071629</t>
+          <t>-0.0032718619869125387 +/- 0.0015282846613521848</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.005175490779298087 +/- 0.0013248695687876429</t>
+          <t>-0.002647233789411052 +/- 0.0011554387031264162</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.0007138607971446054 +/- 0.0004248321492291957</t>
+          <t>-0.00041641879833431705 +/- 0.0003569303985722823</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.0011600237953598657 +/- 0.0007693347505281227</t>
+          <t>0.0004164187983343393 +/- 0.0021905951980394876</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.0006841165972634955 +/- 0.0012481936501104996</t>
+          <t>0.0021415823914336827 +/- 0.0012534983644084104</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.003658536585365901 +/- 0.0007762039470969657</t>
+          <t>-0.0018738845925044489 +/- 0.0011369134356702096</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0023497917906008525 +/- 0.0011400218855881627</t>
+          <t>0.0012790005948839945 +/- 0.0010892226902796277</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.0021713265913147484 +/- 0.0019597342546138264</t>
+          <t>0.0017251635930993548 +/- 0.0017485947003806164</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0007138607971445942 +/- 0.0004832860442971997</t>
+          <t>-0.0013682331945270465 +/- 0.000640709673662641</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.0012492563950030177 +/- 0.002164593146776937</t>
+          <t>0.005205234979179074 +/- 0.0018055978834950839</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.003420582986317711 +/- 0.0016680636398346273</t>
+          <t>-0.00449137418203448 +/- 0.0010678954831062652</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.0021118381915526062 +/- 0.0008967765277621019</t>
+          <t>0.0011897679952409313 +/- 0.0006782721148715773</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.0007138607971445166 +/- 0.0012910490430821315</t>
+          <t>-0.0013682331945270576 +/- 0.0012563183867901635</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.000951814396192785 +/- 0.0005117385643689475</t>
+          <t>-0.0005353955978584235 +/- 0.0004941477610302411</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.9488399762108735e-05 +/- 0.0005612124409313977</t>
+          <t>-0.00026769779892920064 +/- 0.0005395109205002206</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.0020523497917905643 +/- 0.0012151515892811172</t>
+          <t>-0.001070791195716836 +/- 0.0007430098748837971</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.003599048185603848 +/- 0.0015134508308398114</t>
+          <t>-0.0038667459845329933 +/- 0.0017796877217907995</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-0.000535395597858379 +/- 0.0005612124409313872</t>
+          <t>-0.002141582391433672 +/- 0.000984708230651204</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.0011302795954788447 +/- 0.0004941477610302344</t>
+          <t>-0.000743604997025571 +/- 0.0008333685738323632</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.005145746579417054 +/- 0.001493443213638702</t>
+          <t>2.9744199881021062e-05 +/- 0.0015987334503720062</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>5.551115123125783e-17 +/- 0.0008412930174735708</t>
+          <t>0.001814396192742418 +/- 0.0009065883791866771</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.0012790005948840166 +/- 0.0003531928044924766</t>
+          <t>-0.001100535395597868 +/- 0.0007291880233272696</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0010410469958358481 +/- 0.0017305399414382968</t>
+          <t>0.0034800713860797194 +/- 0.0018241223208163915</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.0008030933967875797 +/- 0.0009779465926694566</t>
+          <t>0.0013682331945270687 +/- 0.001506125984672459</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.002409280190362917 +/- 0.001108545220320306</t>
+          <t>-0.001100535395597857 +/- 0.0005492619069785692</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.00014872099940516081 +/- 0.0006684177589007742</t>
+          <t>-0.0027662105889351583 +/- 0.002555405902289518</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0029744199881023394 +/- 0.0014014537762509973</t>
+          <t>-0.0008328375966686563 +/- 0.0023337353058813875</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.002230814991076768 +/- 0.0010152318956499614</t>
+          <t>0.005353955978584191 +/- 0.0007981206344437172</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0027959547888161906 +/- 0.0008641189200674497</t>
+          <t>-0.0005353955978584124 +/- 0.0010952975990197497</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.0015169541939321963 +/- 0.0004501114202980794</t>
+          <t>-0.0008625817965496662 +/- 0.0005228553191923639</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.0033313503866746253 +/- 0.0006886280132534525</t>
+          <t>0.0023497917906008525 +/- 0.001132234759706979</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0016061867935752926 +/- 0.0012060163553071388</t>
+          <t>0.002022605591909599 +/- 0.0015037744984847793</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0008328375966686896 +/- 0.001628070456086124</t>
+          <t>-0.005591909577632359 +/- 0.0015614996726242216</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.007495538370017807 +/- 0.0012030784304673775</t>
+          <t>-0.013057703747769179 +/- 0.0015017139275864972</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.0010707911957167915 +/- 0.0005012581661615966</t>
+          <t>-0.0010113027959547938 +/- 0.0007779117686271365</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0002974419988101884 +/- 0.0004796108119154332</t>
+          <t>-0.0011897679952409313 +/- 0.0005643565128200503</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-0.0006841165972634844 +/- 0.0002676977989291896</t>
+          <t>-0.0001487209994051053 +/- 0.00023980540595770284</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.0025282569898869233 +/- 0.0009239871842361256</t>
+          <t>-0.010707911957168336 +/- 0.0018190225879144092</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.013176680547293318 +/- 0.0022771317127213827</t>
+          <t>-0.002201070791195703 +/- 0.0013513166795479509</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0009518143961927738 +/- 0.0005117385643689682</t>
+          <t>-0.0005353955978584346 +/- 0.0006351622993474914</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.0045508625817966 +/- 0.0010307985396290065</t>
+          <t>0.004669839381320651 +/- 0.0011751782430183503</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>0.0005651397977394668 +/- 0.0015651781221799946</t>
+          <t>-0.017430101130279586 +/- 0.0022106965111317297</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.0012492563950030067 +/- 0.000545220189762719</t>
+          <t>-0.000743604997025582 +/- 0.0005021398874519504</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.004699583581201716 +/- 0.0005117385643689992</t>
+          <t>0.00443188578227246 +/- 0.0011554387031264199</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.009220701963117162 +/- 0.0017086741958768819</t>
+          <t>-0.010232004759071966 +/- 0.002778178329288681</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.0037775133848899746 +/- 0.0015227752214360733</t>
+          <t>0.003807257584770962 +/- 0.0015895763493024805</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.0022903033908388435 +/- 0.0010478236141468402</t>
+          <t>-0.0012492563950029846 +/- 0.0006066650224381451</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>0.0004461629982154047 +/- 0.0002742279731497156</t>
+          <t>-0.0005651397977394334 +/- 0.0003105385636202063</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.00461035098155863 +/- 0.0011841778249490978</t>
+          <t>-0.001130279595478878 +/- 0.0015671552495323412</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>-0.000803093396787602 +/- 0.0018241223208164223</t>
+          <t>0.0031231409875074447 +/- 0.0011766829532928317</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.0002974419988102994 +/- 0.0007285811251586006</t>
+          <t>-0.0008030933967876352 +/- 0.0008828567566719514</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.001695419393218356 +/- 0.0015965183700558697</t>
+          <t>-0.002290303390838777 +/- 0.0009026764369716748</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.003480071386079686 +/- 0.0013698487733098674</t>
+          <t>-0.004312908982748364 +/- 0.0013450825763943915</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-0.0006841165972634955 +/- 0.0011826826503314018</t>
+          <t>0.0027067221891731164 +/- 0.0007577477217642329</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>-0.0002974419988102106 +/- 0.00018811883760667172</t>
+          <t>0.00017846519928612636 +/- 0.00014571622503170743</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.000535395597858468 +/- 0.0003946014027787608</t>
+          <t>0.0024687685901249477 +/- 0.0005805836197484474</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.0019036287923854477 +/- 0.0006124705616292208</t>
+          <t>-0.001070791195716836 +/- 0.0009424734989741088</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,52 +5271,52 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-0.00020820939916713633 +/- 0.0004986036470624578</t>
+          <t>-0.000743604997025582 +/- 0.0012209622695879521</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.0029744199881022726 +/- 0.0011442822166372166</t>
+          <t>-0.004759071980963703 +/- 0.0013823854894256036</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>5.948839976206432e-05 +/- 0.00011897679952412865</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.00041641879833437256 +/- 0.00038091161436246287</t>
+          <t>-0.00020820939916716964 +/- 0.00044217932026527633</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.0013979773944080343 +/- 0.0013954436770660175</t>
+          <t>-0.001814396192742418 +/- 0.001404291687580344</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.0022605591909578004 +/- 0.0011302795954788798</t>
+          <t>-0.0008625817965496662 +/- 0.0015017139275864534</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0010113027959548382 +/- 0.0005353955978584073</t>
+          <t>-0.0013979773944080899 +/- 0.0006657652970136694</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>2.974419988106547e-05 +/- 0.0011164975835290442</t>
+          <t>-0.001992861392028533 +/- 0.000959682677269566</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.0030339083878643926 +/- 0.0014001906360428006</t>
+          <t>0.0015466983938132062 +/- 0.0013154874709991643</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.0007138607971445942 +/- 0.0005516727243007507</t>
+          <t>0.0017549077929803647 +/- 0.0011630704816191237</t>
         </is>
       </c>
     </row>
